--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,82 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -372,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -404,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -439,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -615,2373 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>5.2408274009980903E-2</v>
+        <v>0.05563109121187663</v>
       </c>
       <c r="C2">
-        <v>0.113729490323382</v>
+        <v>0.1141681418988816</v>
       </c>
       <c r="D2">
-        <v>0.13488961348808071</v>
+        <v>0.1350444710473836</v>
       </c>
       <c r="E2">
-        <v>0.1396867988028061</v>
+        <v>0.1349674012921786</v>
       </c>
       <c r="F2">
-        <v>0.19322804833426141</v>
+        <v>0.1884064406164</v>
       </c>
       <c r="G2">
-        <v>0.27633055545652913</v>
+        <v>0.2713196956808726</v>
       </c>
       <c r="H2">
-        <v>0.25877368745291768</v>
+        <v>0.2592310812832144</v>
       </c>
       <c r="I2">
-        <v>0.29818435681559019</v>
+        <v>0.2956790093407661</v>
       </c>
       <c r="J2">
-        <v>0.39624857004213487</v>
+        <v>0.3886617813446304</v>
       </c>
       <c r="K2">
-        <v>0.38585461769067769</v>
+        <v>0.3838680453386868</v>
       </c>
       <c r="L2">
-        <v>0.41230224494526069</v>
+        <v>0.4192172857718998</v>
       </c>
       <c r="M2">
-        <v>0.44730926970413581</v>
+        <v>0.448640543181818</v>
       </c>
       <c r="N2">
-        <v>0.43847786240575931</v>
+        <v>0.438823116296887</v>
       </c>
       <c r="O2">
-        <v>0.42344676571063439</v>
+        <v>0.4247954252031471</v>
       </c>
       <c r="P2">
-        <v>0.4104395344889829</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.408770177648495</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>5.5014414394831401E-2</v>
+        <v>0.05690719771576777</v>
       </c>
       <c r="C3">
-        <v>0.36069539667853079</v>
+        <v>0.3656741634320526</v>
       </c>
       <c r="D3">
-        <v>0.43518580429764281</v>
+        <v>0.434426339568427</v>
       </c>
       <c r="E3">
-        <v>0.3402168720129356</v>
+        <v>0.3389676181624753</v>
       </c>
       <c r="F3">
-        <v>0.34097174601845243</v>
+        <v>0.3329328258166039</v>
       </c>
       <c r="G3">
-        <v>0.34287278919435921</v>
+        <v>0.3452363838127658</v>
       </c>
       <c r="H3">
-        <v>0.37577291359607362</v>
+        <v>0.3828228131874102</v>
       </c>
       <c r="I3">
-        <v>0.40347361818275662</v>
+        <v>0.413622321528216</v>
       </c>
       <c r="J3">
-        <v>0.40074789379982417</v>
+        <v>0.4145014783204052</v>
       </c>
       <c r="K3">
-        <v>0.40502340882743221</v>
+        <v>0.4224512782347168</v>
       </c>
       <c r="L3">
-        <v>0.44103165415203099</v>
+        <v>0.4517401422586612</v>
       </c>
       <c r="M3">
-        <v>0.47800215260402962</v>
+        <v>0.4918428870492673</v>
       </c>
       <c r="N3">
-        <v>0.54280443257536826</v>
+        <v>0.55513267396483</v>
       </c>
       <c r="O3">
-        <v>0.60430961054865906</v>
+        <v>0.6050636996151985</v>
       </c>
       <c r="P3">
-        <v>0.60426253370661609</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.6049074430458261</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>4.5724113999796173E-2</v>
+        <v>0.0449421836207276</v>
       </c>
       <c r="C4">
-        <v>7.37663346514493E-2</v>
+        <v>0.0668850110321679</v>
       </c>
       <c r="D4">
-        <v>0.17460573463858231</v>
+        <v>0.1659928894240691</v>
       </c>
       <c r="E4">
-        <v>0.19764425766874549</v>
+        <v>0.1783569362423504</v>
       </c>
       <c r="F4">
-        <v>0.36082103773660579</v>
+        <v>0.3420239290087844</v>
       </c>
       <c r="G4">
-        <v>0.32468026785889331</v>
+        <v>0.3166177519659896</v>
       </c>
       <c r="H4">
-        <v>0.30314952337475898</v>
+        <v>0.2856403152025805</v>
       </c>
       <c r="I4">
-        <v>0.36938035282353182</v>
+        <v>0.3525720787937667</v>
       </c>
       <c r="J4">
-        <v>0.41092239283410331</v>
+        <v>0.4000416086038752</v>
       </c>
       <c r="K4">
-        <v>0.43158968075396759</v>
+        <v>0.4349110002657961</v>
       </c>
       <c r="L4">
-        <v>0.44457021823648779</v>
+        <v>0.4424470332483899</v>
       </c>
       <c r="M4">
-        <v>0.43702866587951478</v>
+        <v>0.437228718338428</v>
       </c>
       <c r="N4">
-        <v>0.44173270162085121</v>
+        <v>0.4407208696816086</v>
       </c>
       <c r="O4">
-        <v>0.45597165889587821</v>
+        <v>0.4540594255382673</v>
       </c>
       <c r="P4">
-        <v>0.49487924880116152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4903302276268756</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4.207194161902629E-2</v>
+        <v>0.04254617768974436</v>
       </c>
       <c r="C5">
-        <v>0.15749111526623241</v>
+        <v>0.1699115880435274</v>
       </c>
       <c r="D5">
-        <v>0.2103673006125929</v>
+        <v>0.2071950525689907</v>
       </c>
       <c r="E5">
-        <v>0.45653211089298468</v>
+        <v>0.4538816264250834</v>
       </c>
       <c r="F5">
-        <v>0.32348678698329708</v>
+        <v>0.3262911013825802</v>
       </c>
       <c r="G5">
-        <v>0.37676825253387608</v>
+        <v>0.3832365990517081</v>
       </c>
       <c r="H5">
-        <v>0.39184606669425093</v>
+        <v>0.3972745928875172</v>
       </c>
       <c r="I5">
-        <v>0.39412076475075819</v>
+        <v>0.394553167573711</v>
       </c>
       <c r="J5">
-        <v>0.35150447010595232</v>
+        <v>0.356258973089829</v>
       </c>
       <c r="K5">
-        <v>0.35250782456888757</v>
+        <v>0.3555555621927972</v>
       </c>
       <c r="L5">
-        <v>0.35985947351945569</v>
+        <v>0.3702601460736324</v>
       </c>
       <c r="M5">
-        <v>0.37768118006639212</v>
+        <v>0.3944217102994207</v>
       </c>
       <c r="N5">
-        <v>0.42450303781631632</v>
+        <v>0.4473828481461682</v>
       </c>
       <c r="O5">
-        <v>0.4590264315653681</v>
+        <v>0.4849359986018648</v>
       </c>
       <c r="P5">
-        <v>0.51131253026117041</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.5325513475458843</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>4.0312110453458068E-2</v>
+        <v>0.04764650509638872</v>
       </c>
       <c r="C6">
-        <v>0.17965899838822691</v>
+        <v>0.1832078826317479</v>
       </c>
       <c r="D6">
-        <v>0.18424800700239241</v>
+        <v>0.186629706039013</v>
       </c>
       <c r="E6">
-        <v>0.44435217863734189</v>
+        <v>0.4429769980657507</v>
       </c>
       <c r="F6">
-        <v>0.29294316496017009</v>
+        <v>0.2842376428696332</v>
       </c>
       <c r="G6">
-        <v>0.33382416840124141</v>
+        <v>0.3224976662723964</v>
       </c>
       <c r="H6">
-        <v>0.3379235472226037</v>
+        <v>0.3192029394550427</v>
       </c>
       <c r="I6">
-        <v>0.29158089024312189</v>
+        <v>0.2792322794247858</v>
       </c>
       <c r="J6">
-        <v>0.29075328185211141</v>
+        <v>0.2807275689283303</v>
       </c>
       <c r="K6">
-        <v>0.3021524646542329</v>
+        <v>0.2906071650731401</v>
       </c>
       <c r="L6">
-        <v>0.32427192381056091</v>
+        <v>0.3118124417371679</v>
       </c>
       <c r="M6">
-        <v>0.34196199018292511</v>
+        <v>0.3383141829451914</v>
       </c>
       <c r="N6">
-        <v>0.37459731416953451</v>
+        <v>0.3699205888631</v>
       </c>
       <c r="O6">
-        <v>0.38787952270239029</v>
+        <v>0.3839209928119195</v>
       </c>
       <c r="P6">
-        <v>0.4358651544035968</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.4290510674750357</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>4.6614768401833907E-2</v>
+        <v>0.05129048607482597</v>
       </c>
       <c r="C7">
-        <v>7.1368476151506197E-2</v>
+        <v>0.08026916604620872</v>
       </c>
       <c r="D7">
-        <v>0.15330713905754681</v>
+        <v>0.162238012111606</v>
       </c>
       <c r="E7">
-        <v>0.19427168497181921</v>
+        <v>0.204877658112701</v>
       </c>
       <c r="F7">
-        <v>0.32093898050505831</v>
+        <v>0.3265856479808826</v>
       </c>
       <c r="G7">
-        <v>0.36735521614260869</v>
+        <v>0.3756123723689413</v>
       </c>
       <c r="H7">
-        <v>0.32579481522504561</v>
+        <v>0.3348907868581779</v>
       </c>
       <c r="I7">
-        <v>0.30336729052399181</v>
+        <v>0.3017558244949129</v>
       </c>
       <c r="J7">
-        <v>0.36805715318691901</v>
+        <v>0.3701208929894777</v>
       </c>
       <c r="K7">
-        <v>0.40356099619680291</v>
+        <v>0.4095258209927922</v>
       </c>
       <c r="L7">
-        <v>0.43357416587528191</v>
+        <v>0.4476402903214161</v>
       </c>
       <c r="M7">
-        <v>0.45519664476113758</v>
+        <v>0.4678828626805819</v>
       </c>
       <c r="N7">
-        <v>0.42522364911272181</v>
+        <v>0.4359159498800386</v>
       </c>
       <c r="O7">
-        <v>0.44035456073193091</v>
+        <v>0.4430143221153212</v>
       </c>
       <c r="P7">
-        <v>0.45962315310613422</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4633799388125079</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>4.4680455302266719E-2</v>
+        <v>0.04470175764369694</v>
       </c>
       <c r="C8">
-        <v>7.9675587815395257E-2</v>
+        <v>0.07694034708910516</v>
       </c>
       <c r="D8">
-        <v>0.1832486143219666</v>
+        <v>0.174302974153233</v>
       </c>
       <c r="E8">
-        <v>0.33599631028130378</v>
+        <v>0.3311319338950985</v>
       </c>
       <c r="F8">
-        <v>0.32904106850327219</v>
+        <v>0.3175909284541057</v>
       </c>
       <c r="G8">
-        <v>0.28680005088931759</v>
+        <v>0.2896807797711416</v>
       </c>
       <c r="H8">
-        <v>0.32336606785520111</v>
+        <v>0.3288111436757092</v>
       </c>
       <c r="I8">
-        <v>0.34745227646682059</v>
+        <v>0.3477562568975899</v>
       </c>
       <c r="J8">
-        <v>0.35091258779093631</v>
+        <v>0.3606248465013538</v>
       </c>
       <c r="K8">
-        <v>0.37403879821292713</v>
+        <v>0.3772489238440928</v>
       </c>
       <c r="L8">
-        <v>0.40524193328615232</v>
+        <v>0.3966809285322576</v>
       </c>
       <c r="M8">
-        <v>0.39560295070705898</v>
+        <v>0.3934641598669178</v>
       </c>
       <c r="N8">
-        <v>0.38766155620643561</v>
+        <v>0.3885272226696631</v>
       </c>
       <c r="O8">
-        <v>0.40562188288069578</v>
+        <v>0.4049596406593581</v>
       </c>
       <c r="P8">
-        <v>0.43623583959453011</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4399850292092317</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>4.1738221570450741E-2</v>
+        <v>0.03913827910869518</v>
       </c>
       <c r="C9">
-        <v>7.2704498791262215E-2</v>
+        <v>0.07235782064911438</v>
       </c>
       <c r="D9">
-        <v>0.16208710884481101</v>
+        <v>0.1636434530230356</v>
       </c>
       <c r="E9">
-        <v>0.28712950274773769</v>
+        <v>0.2864773018512722</v>
       </c>
       <c r="F9">
-        <v>0.2808455522116598</v>
+        <v>0.2830164762182684</v>
       </c>
       <c r="G9">
-        <v>0.241856762810405</v>
+        <v>0.2420818136605645</v>
       </c>
       <c r="H9">
-        <v>0.27495906014112648</v>
+        <v>0.2683509765283729</v>
       </c>
       <c r="I9">
-        <v>0.27746894628673419</v>
+        <v>0.2722841378063342</v>
       </c>
       <c r="J9">
-        <v>0.27784015695678183</v>
+        <v>0.2756746887423167</v>
       </c>
       <c r="K9">
-        <v>0.28742901364551182</v>
+        <v>0.2809646024966752</v>
       </c>
       <c r="L9">
-        <v>0.32349213417819062</v>
+        <v>0.3167418973636869</v>
       </c>
       <c r="M9">
-        <v>0.29368203630332429</v>
+        <v>0.2888206484321051</v>
       </c>
       <c r="N9">
-        <v>0.29740450107978161</v>
+        <v>0.2908494111471236</v>
       </c>
       <c r="O9">
-        <v>0.30839165892026821</v>
+        <v>0.3076989625299678</v>
       </c>
       <c r="P9">
-        <v>0.32883660751572902</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3277006448445615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>4.6081969136088537E-2</v>
+        <v>0.04742784847370712</v>
       </c>
       <c r="C10">
-        <v>7.9747102533726522E-2</v>
+        <v>0.07592970546860937</v>
       </c>
       <c r="D10">
-        <v>0.1688029657809158</v>
+        <v>0.1655611608253206</v>
       </c>
       <c r="E10">
-        <v>0.30211536513056519</v>
+        <v>0.2965147460019965</v>
       </c>
       <c r="F10">
-        <v>0.29766748949997951</v>
+        <v>0.28863988315657</v>
       </c>
       <c r="G10">
-        <v>0.25100839764587829</v>
+        <v>0.2536556769020608</v>
       </c>
       <c r="H10">
-        <v>0.2803471187553549</v>
+        <v>0.2717997133197901</v>
       </c>
       <c r="I10">
-        <v>0.27374771057817432</v>
+        <v>0.2793942038953015</v>
       </c>
       <c r="J10">
-        <v>0.28415005603637161</v>
+        <v>0.2858822708258912</v>
       </c>
       <c r="K10">
-        <v>0.28556151426004189</v>
+        <v>0.2752615182132011</v>
       </c>
       <c r="L10">
-        <v>0.32990869779418119</v>
+        <v>0.3264273006355155</v>
       </c>
       <c r="M10">
-        <v>0.30265069672826328</v>
+        <v>0.295086384720621</v>
       </c>
       <c r="N10">
-        <v>0.30649314693106833</v>
+        <v>0.2905058778256577</v>
       </c>
       <c r="O10">
-        <v>0.32059674996685722</v>
+        <v>0.3117439654784756</v>
       </c>
       <c r="P10">
-        <v>0.33804552987770098</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3274816490644558</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>4.3039580067829111E-2</v>
+        <v>0.04276718134545309</v>
       </c>
       <c r="C11">
-        <v>7.4321905813371697E-2</v>
+        <v>0.07648880988659185</v>
       </c>
       <c r="D11">
-        <v>0.16771496266108901</v>
+        <v>0.1720536324294984</v>
       </c>
       <c r="E11">
-        <v>0.28562607158038128</v>
+        <v>0.3049550503545098</v>
       </c>
       <c r="F11">
-        <v>0.28905283944492438</v>
+        <v>0.2969331527739561</v>
       </c>
       <c r="G11">
-        <v>0.2473888344394988</v>
+        <v>0.2473660309123886</v>
       </c>
       <c r="H11">
-        <v>0.28286398093247211</v>
+        <v>0.2831893855415532</v>
       </c>
       <c r="I11">
-        <v>0.28381190693660058</v>
+        <v>0.2798800743463626</v>
       </c>
       <c r="J11">
-        <v>0.29166426300751469</v>
+        <v>0.2855788937798665</v>
       </c>
       <c r="K11">
-        <v>0.28380709344683752</v>
+        <v>0.2809568941021485</v>
       </c>
       <c r="L11">
-        <v>0.31205105439831549</v>
+        <v>0.3117011848275796</v>
       </c>
       <c r="M11">
-        <v>0.28899210427401029</v>
+        <v>0.2921491830835297</v>
       </c>
       <c r="N11">
-        <v>0.28638733326778237</v>
+        <v>0.2926963067577533</v>
       </c>
       <c r="O11">
-        <v>0.31124972339837442</v>
+        <v>0.3147100788722646</v>
       </c>
       <c r="P11">
-        <v>0.32192315769201157</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3288105997358367</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>4.91421747050797E-2</v>
+        <v>0.0444761913439795</v>
       </c>
       <c r="C12">
-        <v>0.16713625117627659</v>
+        <v>0.1700666437450545</v>
       </c>
       <c r="D12">
-        <v>0.21224283455858289</v>
+        <v>0.2066130032248917</v>
       </c>
       <c r="E12">
-        <v>0.40361430453395281</v>
+        <v>0.4160587768563994</v>
       </c>
       <c r="F12">
-        <v>0.35171850251923581</v>
+        <v>0.3663780309195002</v>
       </c>
       <c r="G12">
-        <v>0.43794540619586458</v>
+        <v>0.444160183451998</v>
       </c>
       <c r="H12">
-        <v>0.36535362592635789</v>
+        <v>0.3721502157690779</v>
       </c>
       <c r="I12">
-        <v>0.33348411655797572</v>
+        <v>0.3329580972267032</v>
       </c>
       <c r="J12">
-        <v>0.31059547555404737</v>
+        <v>0.3090886126920657</v>
       </c>
       <c r="K12">
-        <v>0.30803424304890259</v>
+        <v>0.3063301053317428</v>
       </c>
       <c r="L12">
-        <v>0.32140470992963099</v>
+        <v>0.3177318220026226</v>
       </c>
       <c r="M12">
-        <v>0.33679684925765269</v>
+        <v>0.3338393672699034</v>
       </c>
       <c r="N12">
-        <v>0.37933896321722138</v>
+        <v>0.3741825266275229</v>
       </c>
       <c r="O12">
-        <v>0.41222204644499461</v>
+        <v>0.4089364514923131</v>
       </c>
       <c r="P12">
-        <v>0.47822949585806479</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4703620992886053</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>5.8126603780969358E-2</v>
+        <v>0.06261050216397603</v>
       </c>
       <c r="C13">
-        <v>0.29496418519166978</v>
+        <v>0.2975907519866996</v>
       </c>
       <c r="D13">
-        <v>0.2977867496069212</v>
+        <v>0.2877311587416513</v>
       </c>
       <c r="E13">
-        <v>0.44584427510714608</v>
+        <v>0.4421020998829689</v>
       </c>
       <c r="F13">
-        <v>0.49253256830226039</v>
+        <v>0.4807896205755515</v>
       </c>
       <c r="G13">
-        <v>0.4748623527560164</v>
+        <v>0.458787874669663</v>
       </c>
       <c r="H13">
-        <v>0.55477811294896939</v>
+        <v>0.5453248621813724</v>
       </c>
       <c r="I13">
-        <v>0.56280535581387003</v>
+        <v>0.5516678025065402</v>
       </c>
       <c r="J13">
-        <v>0.54134513006543405</v>
+        <v>0.5438808607845341</v>
       </c>
       <c r="K13">
-        <v>0.51503152520422835</v>
+        <v>0.5147783048545214</v>
       </c>
       <c r="L13">
-        <v>0.52500574440788972</v>
+        <v>0.5273766197162724</v>
       </c>
       <c r="M13">
-        <v>0.53052748630739521</v>
+        <v>0.5395243343657288</v>
       </c>
       <c r="N13">
-        <v>0.54001595147927151</v>
+        <v>0.5459551209787161</v>
       </c>
       <c r="O13">
-        <v>0.54074032670749506</v>
+        <v>0.5496833579968312</v>
       </c>
       <c r="P13">
-        <v>0.57012715069113018</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.574481191049511</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>4.9447841504039518E-2</v>
+        <v>0.05027095809080804</v>
       </c>
       <c r="C14">
-        <v>7.5609577546818157E-2</v>
+        <v>0.07642322209012464</v>
       </c>
       <c r="D14">
-        <v>0.15344734580728581</v>
+        <v>0.1555281913516285</v>
       </c>
       <c r="E14">
-        <v>0.1856936401860243</v>
+        <v>0.188744501300975</v>
       </c>
       <c r="F14">
-        <v>0.29546676870183702</v>
+        <v>0.3069170741815327</v>
       </c>
       <c r="G14">
-        <v>0.3358343967989057</v>
+        <v>0.3406115334704234</v>
       </c>
       <c r="H14">
-        <v>0.29292233308890658</v>
+        <v>0.3059682287476592</v>
       </c>
       <c r="I14">
-        <v>0.25549386726844958</v>
+        <v>0.2593974302832309</v>
       </c>
       <c r="J14">
-        <v>0.31395728329819628</v>
+        <v>0.3263866469108909</v>
       </c>
       <c r="K14">
-        <v>0.34738921281077778</v>
+        <v>0.3528932582879548</v>
       </c>
       <c r="L14">
-        <v>0.35555512779507958</v>
+        <v>0.3599363194579424</v>
       </c>
       <c r="M14">
-        <v>0.34486019399298162</v>
+        <v>0.3487565035053625</v>
       </c>
       <c r="N14">
-        <v>0.32714737281493578</v>
+        <v>0.3337412098676969</v>
       </c>
       <c r="O14">
-        <v>0.32938689469422061</v>
+        <v>0.3396956056816118</v>
       </c>
       <c r="P14">
-        <v>0.33129424236035371</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3361246407791405</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>5.1494020805196258E-2</v>
+        <v>0.05392207774531405</v>
       </c>
       <c r="C15">
-        <v>7.7149273840052518E-2</v>
+        <v>0.08037960362776039</v>
       </c>
       <c r="D15">
-        <v>0.15778184985792629</v>
+        <v>0.1584588310902402</v>
       </c>
       <c r="E15">
-        <v>0.1894303241427065</v>
+        <v>0.1900384656425244</v>
       </c>
       <c r="F15">
-        <v>0.30355770143739808</v>
+        <v>0.3059757274329106</v>
       </c>
       <c r="G15">
-        <v>0.33516245611988188</v>
+        <v>0.3413622682736192</v>
       </c>
       <c r="H15">
-        <v>0.29802333722261698</v>
+        <v>0.2966005455390077</v>
       </c>
       <c r="I15">
-        <v>0.26438950032782832</v>
+        <v>0.2672207219621753</v>
       </c>
       <c r="J15">
-        <v>0.31324830982114488</v>
+        <v>0.3219843364678084</v>
       </c>
       <c r="K15">
-        <v>0.3546021211527407</v>
+        <v>0.3492516383106664</v>
       </c>
       <c r="L15">
-        <v>0.36746279413515442</v>
+        <v>0.3587061925465609</v>
       </c>
       <c r="M15">
-        <v>0.35399661886448841</v>
+        <v>0.3548177736867306</v>
       </c>
       <c r="N15">
-        <v>0.32878504917524087</v>
+        <v>0.3311109667694382</v>
       </c>
       <c r="O15">
-        <v>0.33225111063780383</v>
+        <v>0.3396110656482245</v>
       </c>
       <c r="P15">
-        <v>0.33759781140864759</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3385779703350842</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>4.6362040573160283E-2</v>
+        <v>0.04664888461001218</v>
       </c>
       <c r="C16">
-        <v>7.4679006473765464E-2</v>
+        <v>0.07326891504712113</v>
       </c>
       <c r="D16">
-        <v>0.1570394134314396</v>
+        <v>0.1521185827590552</v>
       </c>
       <c r="E16">
-        <v>0.19582817962721091</v>
+        <v>0.182514240441684</v>
       </c>
       <c r="F16">
-        <v>0.30892470640236119</v>
+        <v>0.290020099723902</v>
       </c>
       <c r="G16">
-        <v>0.34827434581241201</v>
+        <v>0.3365131760799982</v>
       </c>
       <c r="H16">
-        <v>0.30523593955323403</v>
+        <v>0.3047279497202996</v>
       </c>
       <c r="I16">
-        <v>0.26993276420549439</v>
+        <v>0.2571377862722082</v>
       </c>
       <c r="J16">
-        <v>0.32123734040782481</v>
+        <v>0.3051574331953158</v>
       </c>
       <c r="K16">
-        <v>0.3609334085854401</v>
+        <v>0.3417476173633764</v>
       </c>
       <c r="L16">
-        <v>0.36909813490238569</v>
+        <v>0.3595511662701078</v>
       </c>
       <c r="M16">
-        <v>0.35652667429867058</v>
+        <v>0.3522203621096303</v>
       </c>
       <c r="N16">
-        <v>0.33540389263247078</v>
+        <v>0.3240611020332523</v>
       </c>
       <c r="O16">
-        <v>0.33589391182551781</v>
+        <v>0.3249415704943839</v>
       </c>
       <c r="P16">
-        <v>0.32795711790391679</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.3297103471131173</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>4.7228476809482098E-2</v>
+        <v>0.0479064310087228</v>
       </c>
       <c r="C17">
-        <v>7.6205255860020332E-2</v>
+        <v>0.07686522950475091</v>
       </c>
       <c r="D17">
-        <v>0.1546875349524135</v>
+        <v>0.1576864453582562</v>
       </c>
       <c r="E17">
-        <v>0.1928692074430815</v>
+        <v>0.191013894355692</v>
       </c>
       <c r="F17">
-        <v>0.30007243313661108</v>
+        <v>0.289548863418194</v>
       </c>
       <c r="G17">
-        <v>0.33545367302568951</v>
+        <v>0.3366530547772575</v>
       </c>
       <c r="H17">
-        <v>0.30028679691086008</v>
+        <v>0.2971437442784969</v>
       </c>
       <c r="I17">
-        <v>0.25805018543420549</v>
+        <v>0.2458337094779826</v>
       </c>
       <c r="J17">
-        <v>0.31285009487886689</v>
+        <v>0.3042249333866945</v>
       </c>
       <c r="K17">
-        <v>0.3555046624521942</v>
+        <v>0.3464284633457698</v>
       </c>
       <c r="L17">
-        <v>0.37295543840662809</v>
+        <v>0.3671391756407908</v>
       </c>
       <c r="M17">
-        <v>0.35909764733319283</v>
+        <v>0.3521233180816134</v>
       </c>
       <c r="N17">
-        <v>0.33822471990533842</v>
+        <v>0.3436127231159531</v>
       </c>
       <c r="O17">
-        <v>0.33973133560059848</v>
+        <v>0.3500620387040659</v>
       </c>
       <c r="P17">
-        <v>0.34049790916929801</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.3533993865842958</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>4.6082367400866978E-2</v>
+        <v>0.04304763026957641</v>
       </c>
       <c r="C18">
-        <v>0.16606864299325649</v>
+        <v>0.1735714312457761</v>
       </c>
       <c r="D18">
-        <v>0.2235880280196495</v>
+        <v>0.2151166860059246</v>
       </c>
       <c r="E18">
-        <v>0.43009524398128829</v>
+        <v>0.433445309185141</v>
       </c>
       <c r="F18">
-        <v>0.34405634944478181</v>
+        <v>0.3318260239118914</v>
       </c>
       <c r="G18">
-        <v>0.40477615640771608</v>
+        <v>0.3939112472911001</v>
       </c>
       <c r="H18">
-        <v>0.44458151355555903</v>
+        <v>0.4380192541253982</v>
       </c>
       <c r="I18">
-        <v>0.37986998377534192</v>
+        <v>0.3757840428054818</v>
       </c>
       <c r="J18">
-        <v>0.32872972579345322</v>
+        <v>0.3272513172692609</v>
       </c>
       <c r="K18">
-        <v>0.31447918656113838</v>
+        <v>0.318185148433376</v>
       </c>
       <c r="L18">
-        <v>0.34231012915523051</v>
+        <v>0.340910048068931</v>
       </c>
       <c r="M18">
-        <v>0.35865516926376378</v>
+        <v>0.3532559724747233</v>
       </c>
       <c r="N18">
-        <v>0.40788395029031682</v>
+        <v>0.4072002027541484</v>
       </c>
       <c r="O18">
-        <v>0.45070894953531898</v>
+        <v>0.4520461519661561</v>
       </c>
       <c r="P18">
-        <v>0.49102076440231629</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4940222878048771</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>4.5991416582942792E-2</v>
+        <v>0.04417430208801205</v>
       </c>
       <c r="C19">
-        <v>0.1906084207625402</v>
+        <v>0.1958710567660968</v>
       </c>
       <c r="D19">
-        <v>0.2087277354436948</v>
+        <v>0.2109897303077424</v>
       </c>
       <c r="E19">
-        <v>0.44678318629391101</v>
+        <v>0.4617027682871863</v>
       </c>
       <c r="F19">
-        <v>0.29129699083395932</v>
+        <v>0.3020456258756535</v>
       </c>
       <c r="G19">
-        <v>0.30865054675808529</v>
+        <v>0.3174250610331317</v>
       </c>
       <c r="H19">
-        <v>0.27922257264289102</v>
+        <v>0.2820043288851229</v>
       </c>
       <c r="I19">
-        <v>0.26453805795372892</v>
+        <v>0.2684348563767193</v>
       </c>
       <c r="J19">
-        <v>0.2562681998897483</v>
+        <v>0.2655374724131538</v>
       </c>
       <c r="K19">
-        <v>0.27632911225161999</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.30558014067478367</v>
+        <v>0.2844623695912796</v>
+      </c>
+      <c r="L19">
+        <v>0.3087968769426582</v>
       </c>
       <c r="M19">
-        <v>0.33304049583574702</v>
+        <v>0.3327964419287649</v>
       </c>
       <c r="N19">
-        <v>0.37764416186767308</v>
+        <v>0.3705356140094986</v>
       </c>
       <c r="O19">
-        <v>0.38398327809673938</v>
+        <v>0.381987476917319</v>
       </c>
       <c r="P19">
-        <v>0.41773652972648562</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4193121638008005</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.5673206265316527E-2</v>
+        <v>0.04284921055280405</v>
       </c>
       <c r="C20">
-        <v>0.2451819557002797</v>
+        <v>0.2339946617047225</v>
       </c>
       <c r="D20">
-        <v>0.22591216804360389</v>
+        <v>0.2269782832932367</v>
       </c>
       <c r="E20">
-        <v>0.25419034875033131</v>
+        <v>0.2584665591535685</v>
       </c>
       <c r="F20">
-        <v>0.24140494433172111</v>
+        <v>0.2541150575331637</v>
       </c>
       <c r="G20">
-        <v>0.3132572213555157</v>
+        <v>0.3376126165980769</v>
       </c>
       <c r="H20">
-        <v>0.27680466548409149</v>
+        <v>0.2911449608697473</v>
       </c>
       <c r="I20">
-        <v>0.27235619821897122</v>
+        <v>0.2821159710633154</v>
       </c>
       <c r="J20">
-        <v>0.25904436742496162</v>
+        <v>0.2662891773550174</v>
       </c>
       <c r="K20">
-        <v>0.27765983675994182</v>
+        <v>0.2895538165060705</v>
       </c>
       <c r="L20">
-        <v>0.30698288191009809</v>
+        <v>0.3160419586963638</v>
       </c>
       <c r="M20">
-        <v>0.33927167773721267</v>
+        <v>0.3502621071878617</v>
       </c>
       <c r="N20">
-        <v>0.3185881260683821</v>
+        <v>0.3307697432820608</v>
       </c>
       <c r="O20">
-        <v>0.34136890189996177</v>
+        <v>0.3531120088106151</v>
       </c>
       <c r="P20">
-        <v>0.35523317152156098</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3743896187317931</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>5.8471572305564178E-2</v>
+        <v>0.05653671480929612</v>
       </c>
       <c r="C21">
-        <v>0.33126251910423582</v>
+        <v>0.338060457377255</v>
       </c>
       <c r="D21">
-        <v>0.39029798671930072</v>
+        <v>0.4042615311971539</v>
       </c>
       <c r="E21">
-        <v>0.3079422032885572</v>
+        <v>0.3335062605363162</v>
       </c>
       <c r="F21">
-        <v>0.31842596867096568</v>
+        <v>0.3326134881511972</v>
       </c>
       <c r="G21">
-        <v>0.36566656344942311</v>
+        <v>0.3752173042017648</v>
       </c>
       <c r="H21">
-        <v>0.42811097127184727</v>
+        <v>0.4292435262687698</v>
       </c>
       <c r="I21">
-        <v>0.44188497332565557</v>
+        <v>0.4609472623731069</v>
       </c>
       <c r="J21">
-        <v>0.4343646448962708</v>
+        <v>0.4328565958281419</v>
       </c>
       <c r="K21">
-        <v>0.43813459024981161</v>
+        <v>0.4434765708249784</v>
       </c>
       <c r="L21">
-        <v>0.45544902525354469</v>
+        <v>0.4595674181720639</v>
       </c>
       <c r="M21">
-        <v>0.5008033624816064</v>
+        <v>0.5028969284896094</v>
       </c>
       <c r="N21">
-        <v>0.57142897400530801</v>
+        <v>0.5656593334519245</v>
       </c>
       <c r="O21">
-        <v>0.63424711194023597</v>
+        <v>0.626010475226663</v>
       </c>
       <c r="P21">
-        <v>0.64583591613915126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.6355569504279894</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>5.3183115662624153E-2</v>
+        <v>0.05644391737128923</v>
       </c>
       <c r="C22">
-        <v>0.33138590313558952</v>
+        <v>0.336553835544928</v>
       </c>
       <c r="D22">
-        <v>0.38348091326011591</v>
+        <v>0.3948563566249144</v>
       </c>
       <c r="E22">
-        <v>0.3089778063504301</v>
+        <v>0.308804025987394</v>
       </c>
       <c r="F22">
-        <v>0.31056392173891839</v>
+        <v>0.3147724370078923</v>
       </c>
       <c r="G22">
-        <v>0.35568286443260988</v>
+        <v>0.359405158993915</v>
       </c>
       <c r="H22">
-        <v>0.43197124054244418</v>
+        <v>0.4359646447975307</v>
       </c>
       <c r="I22">
-        <v>0.47431979902319321</v>
+        <v>0.4849489258923367</v>
       </c>
       <c r="J22">
-        <v>0.46370565268617192</v>
+        <v>0.4744710263679418</v>
       </c>
       <c r="K22">
-        <v>0.46698217180488721</v>
+        <v>0.4827262931210595</v>
       </c>
       <c r="L22">
-        <v>0.50641830700040513</v>
+        <v>0.5206850334384708</v>
       </c>
       <c r="M22">
-        <v>0.53344941630348175</v>
+        <v>0.5484138366106823</v>
       </c>
       <c r="N22">
-        <v>0.58427040784803408</v>
+        <v>0.6012456621385575</v>
       </c>
       <c r="O22">
-        <v>0.60975957480238918</v>
+        <v>0.6271378139626059</v>
       </c>
       <c r="P22">
-        <v>0.62849993641140534</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.6461711709746838</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>4.9275483418204459E-2</v>
+        <v>0.044867470039565</v>
       </c>
       <c r="C23">
-        <v>0.2655210963006171</v>
+        <v>0.2622818540564527</v>
       </c>
       <c r="D23">
-        <v>0.2851781904569578</v>
+        <v>0.2650069795290621</v>
       </c>
       <c r="E23">
-        <v>0.21882548349633621</v>
+        <v>0.2181585693451353</v>
       </c>
       <c r="F23">
-        <v>0.29510983946670161</v>
+        <v>0.2884794746959232</v>
       </c>
       <c r="G23">
-        <v>0.28907656205859489</v>
+        <v>0.2833511991024186</v>
       </c>
       <c r="H23">
-        <v>0.30576649595960381</v>
+        <v>0.301482298919881</v>
       </c>
       <c r="I23">
-        <v>0.35015751550684859</v>
+        <v>0.3450827149249732</v>
       </c>
       <c r="J23">
-        <v>0.36598996624453722</v>
+        <v>0.3662614776156696</v>
       </c>
       <c r="K23">
-        <v>0.42724250558457422</v>
+        <v>0.431541371722604</v>
       </c>
       <c r="L23">
-        <v>0.46027770580206678</v>
+        <v>0.4677317180054811</v>
       </c>
       <c r="M23">
-        <v>0.52493486656480615</v>
+        <v>0.5297507855581582</v>
       </c>
       <c r="N23">
-        <v>0.54533007551436152</v>
+        <v>0.5515475809591415</v>
       </c>
       <c r="O23">
-        <v>0.56187126289945066</v>
+        <v>0.5687978068628967</v>
       </c>
       <c r="P23">
-        <v>0.59827380070251612</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.6024408876620548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.1031939764810621</v>
+        <v>0.103410919829069</v>
       </c>
       <c r="C24">
-        <v>0.14692781836832891</v>
+        <v>0.1469524185218946</v>
       </c>
       <c r="D24">
-        <v>0.18974079208151051</v>
+        <v>0.1977443190989291</v>
       </c>
       <c r="E24">
-        <v>0.28876950834545417</v>
+        <v>0.2964798032407697</v>
       </c>
       <c r="F24">
-        <v>0.3831144515115551</v>
+        <v>0.3894485419447791</v>
       </c>
       <c r="G24">
-        <v>0.57004624324035669</v>
+        <v>0.5807821546342696</v>
       </c>
       <c r="H24">
-        <v>0.59521512256054931</v>
+        <v>0.6054864430544087</v>
       </c>
       <c r="I24">
-        <v>0.68234949479207652</v>
+        <v>0.6949531437266794</v>
       </c>
       <c r="J24">
-        <v>0.79627943936240664</v>
+        <v>0.807396382918422</v>
       </c>
       <c r="K24">
-        <v>0.99765539940101022</v>
+        <v>1.008876905866965</v>
       </c>
       <c r="L24">
-        <v>1.001779851912463</v>
+        <v>1.023589330527837</v>
       </c>
       <c r="M24">
-        <v>1.077530634112883</v>
+        <v>1.099647301209441</v>
       </c>
       <c r="N24">
-        <v>1.198407519540083</v>
+        <v>1.228509155281901</v>
       </c>
       <c r="O24">
-        <v>1.300244763972944</v>
+        <v>1.331146139927539</v>
       </c>
       <c r="P24">
-        <v>1.455668124411599</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>1.471373251064127</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.2473553543479276</v>
+        <v>0.2382746641053779</v>
       </c>
       <c r="C25">
-        <v>0.35380454470271611</v>
+        <v>0.3444317422076331</v>
       </c>
       <c r="D25">
-        <v>0.40300227067362981</v>
+        <v>0.3954122272763885</v>
       </c>
       <c r="E25">
-        <v>0.4117088121756185</v>
+        <v>0.4093038213081669</v>
       </c>
       <c r="F25">
-        <v>0.62814842448265162</v>
+        <v>0.6148450878934525</v>
       </c>
       <c r="G25">
-        <v>0.7530722725030552</v>
+        <v>0.7367066031030418</v>
       </c>
       <c r="H25">
-        <v>0.79913471073846631</v>
+        <v>0.7900602188212056</v>
       </c>
       <c r="I25">
-        <v>0.81998969324845628</v>
+        <v>0.8153819312873282</v>
       </c>
       <c r="J25">
-        <v>0.88268495492811727</v>
+        <v>0.8842218272049923</v>
       </c>
       <c r="K25">
-        <v>1.0191282916776041</v>
+        <v>1.027560154489822</v>
       </c>
       <c r="L25">
-        <v>1.102169456321564</v>
+        <v>1.114209500206629</v>
       </c>
       <c r="M25">
-        <v>1.235503414218005</v>
+        <v>1.25034107070512</v>
       </c>
       <c r="N25">
-        <v>1.3725123689024661</v>
+        <v>1.39136208683369</v>
       </c>
       <c r="O25">
-        <v>1.4570900184360851</v>
+        <v>1.473406456493909</v>
       </c>
       <c r="P25">
-        <v>1.5250472990494059</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>1.530448475729935</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>9.740835825944355E-2</v>
+        <v>0.09908485819786705</v>
       </c>
       <c r="C26">
-        <v>0.15752318763808401</v>
+        <v>0.1550102912703344</v>
       </c>
       <c r="D26">
-        <v>0.12668905003658429</v>
+        <v>0.130508687804385</v>
       </c>
       <c r="E26">
-        <v>0.14004903067178889</v>
+        <v>0.1436021321381574</v>
       </c>
       <c r="F26">
-        <v>0.24721147808387281</v>
+        <v>0.2495483526458516</v>
       </c>
       <c r="G26">
-        <v>0.24826457105697269</v>
+        <v>0.2568331439127736</v>
       </c>
       <c r="H26">
-        <v>0.27326343708325729</v>
+        <v>0.2823304008278617</v>
       </c>
       <c r="I26">
-        <v>0.34547517053568078</v>
+        <v>0.3427872652500855</v>
       </c>
       <c r="J26">
-        <v>0.35626769055471041</v>
+        <v>0.3576756294268331</v>
       </c>
       <c r="K26">
-        <v>0.41294863269869309</v>
+        <v>0.4051328874395748</v>
       </c>
       <c r="L26">
-        <v>0.4626507972295435</v>
+        <v>0.4578310447640841</v>
       </c>
       <c r="M26">
-        <v>0.4798773690376279</v>
+        <v>0.4727284300345447</v>
       </c>
       <c r="N26">
-        <v>0.52615594676355981</v>
+        <v>0.5318862209634109</v>
       </c>
       <c r="O26">
-        <v>0.61224465256226501</v>
+        <v>0.6094031571596334</v>
       </c>
       <c r="P26">
-        <v>0.63950813050067035</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.6407557102476867</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.16706419081957649</v>
+        <v>0.162064690397171</v>
       </c>
       <c r="C27">
-        <v>0.32045499041166092</v>
+        <v>0.3173437248974593</v>
       </c>
       <c r="D27">
-        <v>0.15081103113232719</v>
+        <v>0.1505623269748936</v>
       </c>
       <c r="E27">
-        <v>0.15997380764290131</v>
+        <v>0.1739876293255878</v>
       </c>
       <c r="F27">
-        <v>0.26410219390441197</v>
+        <v>0.2662164903437321</v>
       </c>
       <c r="G27">
-        <v>0.33017987536041538</v>
+        <v>0.3318972199762984</v>
       </c>
       <c r="H27">
-        <v>0.40190997179310711</v>
+        <v>0.403210064835113</v>
       </c>
       <c r="I27">
-        <v>0.5474410043676935</v>
+        <v>0.5372374205235193</v>
       </c>
       <c r="J27">
-        <v>0.57545648574343811</v>
+        <v>0.5698576597860578</v>
       </c>
       <c r="K27">
-        <v>0.59789717326700009</v>
+        <v>0.5959062082355955</v>
       </c>
       <c r="L27">
-        <v>0.57322330082722051</v>
+        <v>0.5800082036153495</v>
       </c>
       <c r="M27">
-        <v>0.57371585837579486</v>
+        <v>0.5778430484343948</v>
       </c>
       <c r="N27">
-        <v>0.60372743704143317</v>
+        <v>0.6028297601976964</v>
       </c>
       <c r="O27">
-        <v>0.65721181928663908</v>
+        <v>0.65564813045554</v>
       </c>
       <c r="P27">
-        <v>0.69539532558875772</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.6864757634299279</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>6.6602283951883959E-2</v>
+        <v>0.0657076431518607</v>
       </c>
       <c r="C28">
-        <v>0.1230366003820058</v>
+        <v>0.1260303665767638</v>
       </c>
       <c r="D28">
-        <v>0.21952513821830619</v>
+        <v>0.2173803768906239</v>
       </c>
       <c r="E28">
-        <v>0.20881124361886641</v>
+        <v>0.2095863268687895</v>
       </c>
       <c r="F28">
-        <v>0.2210260667216179</v>
+        <v>0.225428586586474</v>
       </c>
       <c r="G28">
-        <v>0.2143088617613356</v>
+        <v>0.2137667510850345</v>
       </c>
       <c r="H28">
-        <v>0.3067868988239692</v>
+        <v>0.3045445112060172</v>
       </c>
       <c r="I28">
-        <v>0.44300433960782731</v>
+        <v>0.4374643034388472</v>
       </c>
       <c r="J28">
-        <v>0.473859029453082</v>
+        <v>0.4846305620308964</v>
       </c>
       <c r="K28">
-        <v>0.46459635526981607</v>
+        <v>0.4613885173323252</v>
       </c>
       <c r="L28">
-        <v>0.47944336651951669</v>
+        <v>0.4767105780082173</v>
       </c>
       <c r="M28">
-        <v>0.56978983162857477</v>
+        <v>0.5735437919186892</v>
       </c>
       <c r="N28">
-        <v>0.67814493296758016</v>
+        <v>0.679890046111939</v>
       </c>
       <c r="O28">
-        <v>0.76074002028171461</v>
+        <v>0.7591500910769088</v>
       </c>
       <c r="P28">
-        <v>0.86243512181539528</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.8686535830839194</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>7.3280630697434207E-2</v>
+        <v>0.07468248532633809</v>
       </c>
       <c r="C29">
-        <v>0.13909679203366079</v>
+        <v>0.1371200004455144</v>
       </c>
       <c r="D29">
-        <v>0.24412153509201551</v>
+        <v>0.2419853731229921</v>
       </c>
       <c r="E29">
-        <v>0.23420966483259689</v>
+        <v>0.2322481430235171</v>
       </c>
       <c r="F29">
-        <v>0.2153616686273383</v>
+        <v>0.2193739351826486</v>
       </c>
       <c r="G29">
-        <v>0.24437044738025709</v>
+        <v>0.2470775924296489</v>
       </c>
       <c r="H29">
-        <v>0.54075168006617624</v>
+        <v>0.5331670501908716</v>
       </c>
       <c r="I29">
-        <v>0.53415759283756159</v>
+        <v>0.5106857265402859</v>
       </c>
       <c r="J29">
-        <v>0.51095442869727647</v>
+        <v>0.5036161824609835</v>
       </c>
       <c r="K29">
-        <v>0.48016698014620163</v>
+        <v>0.4850284201896571</v>
       </c>
       <c r="L29">
-        <v>0.48913719731722322</v>
+        <v>0.4860207788085373</v>
       </c>
       <c r="M29">
-        <v>0.52373122982823939</v>
+        <v>0.5190219676826057</v>
       </c>
       <c r="N29">
-        <v>0.60284362518482548</v>
+        <v>0.5983961790846561</v>
       </c>
       <c r="O29">
-        <v>0.6975257823173725</v>
+        <v>0.6919327640742702</v>
       </c>
       <c r="P29">
-        <v>0.78774130619495131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.7774953912884071</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>8.0339660867348728E-2</v>
+        <v>0.07758479740413199</v>
       </c>
       <c r="C30">
-        <v>0.15404786953315361</v>
+        <v>0.1477783894804692</v>
       </c>
       <c r="D30">
-        <v>0.2072981438024798</v>
+        <v>0.1954179996675209</v>
       </c>
       <c r="E30">
-        <v>0.19536096197328881</v>
+        <v>0.1865370027127151</v>
       </c>
       <c r="F30">
-        <v>0.25411850628529209</v>
+        <v>0.2578919042542827</v>
       </c>
       <c r="G30">
-        <v>0.26085966667022442</v>
+        <v>0.2590709905417385</v>
       </c>
       <c r="H30">
-        <v>0.36893439108699772</v>
+        <v>0.3802942786134278</v>
       </c>
       <c r="I30">
-        <v>0.60775350483287793</v>
+        <v>0.6124978789854455</v>
       </c>
       <c r="J30">
-        <v>0.49961631350766961</v>
+        <v>0.5100035050664896</v>
       </c>
       <c r="K30">
-        <v>0.50733784950900185</v>
+        <v>0.5096379848084001</v>
       </c>
       <c r="L30">
-        <v>0.55075671078383315</v>
+        <v>0.5436397633094951</v>
       </c>
       <c r="M30">
-        <v>0.64617039061353054</v>
+        <v>0.631651867612016</v>
       </c>
       <c r="N30">
-        <v>0.71950245965892512</v>
+        <v>0.699920596442291</v>
       </c>
       <c r="O30">
-        <v>0.79776556191158821</v>
+        <v>0.7830821826943373</v>
       </c>
       <c r="P30">
-        <v>0.90859429024849347</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.8949066584320959</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>7.5607725159523562E-2</v>
+        <v>0.07737038176184435</v>
       </c>
       <c r="C31">
-        <v>0.14708847506007131</v>
+        <v>0.1536156929089883</v>
       </c>
       <c r="D31">
-        <v>0.19064381137374409</v>
+        <v>0.1993376768644302</v>
       </c>
       <c r="E31">
-        <v>0.1790251421734125</v>
+        <v>0.1817555574917584</v>
       </c>
       <c r="F31">
-        <v>0.22831351570419339</v>
+        <v>0.2348279213259655</v>
       </c>
       <c r="G31">
-        <v>0.22578828308966939</v>
+        <v>0.2317595111294339</v>
       </c>
       <c r="H31">
-        <v>0.25856230969692612</v>
+        <v>0.2593564178992172</v>
       </c>
       <c r="I31">
-        <v>0.43927689386514618</v>
+        <v>0.4598751958399043</v>
       </c>
       <c r="J31">
-        <v>0.36964400348601412</v>
+        <v>0.3754785819258645</v>
       </c>
       <c r="K31">
-        <v>0.35636176338309389</v>
+        <v>0.3517958060790226</v>
       </c>
       <c r="L31">
-        <v>0.33846812939855458</v>
+        <v>0.3323929231091368</v>
       </c>
       <c r="M31">
-        <v>0.38669118567766553</v>
+        <v>0.378375934324438</v>
       </c>
       <c r="N31">
-        <v>0.39127740083358148</v>
+        <v>0.3831709942382091</v>
       </c>
       <c r="O31">
-        <v>0.44576036918108319</v>
+        <v>0.4292543326040636</v>
       </c>
       <c r="P31">
-        <v>0.47047509906106399</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.4523595033560244</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>7.199518143522729E-2</v>
+        <v>0.07113976980825909</v>
       </c>
       <c r="C32">
-        <v>0.13999553181364049</v>
+        <v>0.1313181084993425</v>
       </c>
       <c r="D32">
-        <v>0.23204169348323311</v>
+        <v>0.2284926266424842</v>
       </c>
       <c r="E32">
-        <v>0.22154720430897959</v>
+        <v>0.2125582493868606</v>
       </c>
       <c r="F32">
-        <v>0.2043387670222129</v>
+        <v>0.2008162056782986</v>
       </c>
       <c r="G32">
-        <v>0.21893826309644041</v>
+        <v>0.2179788691036536</v>
       </c>
       <c r="H32">
-        <v>0.39671361180694648</v>
+        <v>0.3984366198419584</v>
       </c>
       <c r="I32">
-        <v>0.39621825535584038</v>
+        <v>0.3976997469546545</v>
       </c>
       <c r="J32">
-        <v>0.37921756084359393</v>
+        <v>0.3857470137800002</v>
       </c>
       <c r="K32">
-        <v>0.35568884455512412</v>
+        <v>0.3612108294753101</v>
       </c>
       <c r="L32">
-        <v>0.34839791245459578</v>
+        <v>0.346523784853895</v>
       </c>
       <c r="M32">
-        <v>0.34612829464312239</v>
+        <v>0.3435030300022969</v>
       </c>
       <c r="N32">
-        <v>0.38907760161994548</v>
+        <v>0.3746004528909045</v>
       </c>
       <c r="O32">
-        <v>0.42437117439554778</v>
+        <v>0.4168563035671892</v>
       </c>
       <c r="P32">
-        <v>0.46231819447083389</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.445447292660769</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>7.4167492444816879E-2</v>
+        <v>0.07291164992198113</v>
       </c>
       <c r="C33">
-        <v>0.14004656549648339</v>
+        <v>0.1363594970330548</v>
       </c>
       <c r="D33">
-        <v>0.23674125095281889</v>
+        <v>0.2318248385578142</v>
       </c>
       <c r="E33">
-        <v>0.2207396981986442</v>
+        <v>0.2164387876714763</v>
       </c>
       <c r="F33">
-        <v>0.20371764399313039</v>
+        <v>0.2026380757716171</v>
       </c>
       <c r="G33">
-        <v>0.21655288150004531</v>
+        <v>0.2094453963340044</v>
       </c>
       <c r="H33">
-        <v>0.39602244222536948</v>
+        <v>0.3800266282309782</v>
       </c>
       <c r="I33">
-        <v>0.38966856980516218</v>
+        <v>0.377875468546009</v>
       </c>
       <c r="J33">
-        <v>0.3785670862074153</v>
+        <v>0.3700411346476445</v>
       </c>
       <c r="K33">
-        <v>0.33466761609741869</v>
+        <v>0.3232703502189118</v>
       </c>
       <c r="L33">
-        <v>0.33087150281882749</v>
+        <v>0.3247536766155171</v>
       </c>
       <c r="M33">
-        <v>0.31821982212547623</v>
+        <v>0.3202848228116948</v>
       </c>
       <c r="N33">
-        <v>0.35746952159992029</v>
+        <v>0.3531826004839728</v>
       </c>
       <c r="O33">
-        <v>0.38589925205223419</v>
+        <v>0.3826042064094256</v>
       </c>
       <c r="P33">
-        <v>0.41602955126802932</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.4069067440229487</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>7.090628664271674E-2</v>
+        <v>0.06729292389907937</v>
       </c>
       <c r="C34">
-        <v>0.13574514424303449</v>
+        <v>0.130144977018025</v>
       </c>
       <c r="D34">
-        <v>0.22973934575292629</v>
+        <v>0.2286429120521201</v>
       </c>
       <c r="E34">
-        <v>0.21582322464693959</v>
+        <v>0.2152697402200889</v>
       </c>
       <c r="F34">
-        <v>0.207236659769268</v>
+        <v>0.195820673577404</v>
       </c>
       <c r="G34">
-        <v>0.2148835278612794</v>
+        <v>0.2054304411093182</v>
       </c>
       <c r="H34">
-        <v>0.38037843900198931</v>
+        <v>0.3731379758075806</v>
       </c>
       <c r="I34">
-        <v>0.38433962681610201</v>
+        <v>0.382621245177735</v>
       </c>
       <c r="J34">
-        <v>0.37784244692709479</v>
+        <v>0.3799216517510873</v>
       </c>
       <c r="K34">
-        <v>0.33196835266492691</v>
+        <v>0.336337589083875</v>
       </c>
       <c r="L34">
-        <v>0.33484424652411182</v>
+        <v>0.3334113508925771</v>
       </c>
       <c r="M34">
-        <v>0.31708076018096398</v>
+        <v>0.323078517808761</v>
       </c>
       <c r="N34">
-        <v>0.36256030622226237</v>
+        <v>0.3639164966006937</v>
       </c>
       <c r="O34">
-        <v>0.39078544302819168</v>
+        <v>0.3906883148304188</v>
       </c>
       <c r="P34">
-        <v>0.419824024681202</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.4145929276672173</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>7.8168567379392581E-2</v>
+        <v>0.07036447400021924</v>
       </c>
       <c r="C35">
-        <v>0.14504299124460401</v>
+        <v>0.1370193552139108</v>
       </c>
       <c r="D35">
-        <v>0.2392636737936156</v>
+        <v>0.2329697309418059</v>
       </c>
       <c r="E35">
-        <v>0.224242316217174</v>
+        <v>0.2173407358820298</v>
       </c>
       <c r="F35">
-        <v>0.21336899802908049</v>
+        <v>0.2053752854557724</v>
       </c>
       <c r="G35">
-        <v>0.2177608220387186</v>
+        <v>0.2162902393863992</v>
       </c>
       <c r="H35">
-        <v>0.37123925633082272</v>
+        <v>0.3708744471870631</v>
       </c>
       <c r="I35">
-        <v>0.38413566558019652</v>
+        <v>0.390640623115628</v>
       </c>
       <c r="J35">
-        <v>0.39463213771463279</v>
+        <v>0.3961199267927493</v>
       </c>
       <c r="K35">
-        <v>0.33790664470807508</v>
+        <v>0.3470206908936629</v>
       </c>
       <c r="L35">
-        <v>0.34400089017187219</v>
+        <v>0.3471870712000749</v>
       </c>
       <c r="M35">
-        <v>0.3310457205977565</v>
+        <v>0.3333134366057895</v>
       </c>
       <c r="N35">
-        <v>0.36077068029816389</v>
+        <v>0.3618442912181865</v>
       </c>
       <c r="O35">
-        <v>0.39057261388305953</v>
+        <v>0.3944303680798881</v>
       </c>
       <c r="P35">
-        <v>0.40194480973892072</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.4021954498267153</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>7.0684246575086929E-2</v>
+        <v>0.07473056995451291</v>
       </c>
       <c r="C36">
-        <v>0.1353857217351272</v>
+        <v>0.1453555661660083</v>
       </c>
       <c r="D36">
-        <v>0.2324378981767746</v>
+        <v>0.2389773942009833</v>
       </c>
       <c r="E36">
-        <v>0.22234095236274501</v>
+        <v>0.221996289675337</v>
       </c>
       <c r="F36">
-        <v>0.2040673159883902</v>
+        <v>0.213242358240208</v>
       </c>
       <c r="G36">
-        <v>0.22389720245026881</v>
+        <v>0.229941011046014</v>
       </c>
       <c r="H36">
-        <v>0.41903371159852532</v>
+        <v>0.4357483394134021</v>
       </c>
       <c r="I36">
-        <v>0.41014242673651541</v>
+        <v>0.4169324684827614</v>
       </c>
       <c r="J36">
-        <v>0.39299362118181269</v>
+        <v>0.4044252323491577</v>
       </c>
       <c r="K36">
-        <v>0.36839259186591577</v>
+        <v>0.367864191286109</v>
       </c>
       <c r="L36">
-        <v>0.36052814833475388</v>
+        <v>0.3636656687322294</v>
       </c>
       <c r="M36">
-        <v>0.36516914312176862</v>
+        <v>0.3549039319481165</v>
       </c>
       <c r="N36">
-        <v>0.40647899951918581</v>
+        <v>0.3994495361098805</v>
       </c>
       <c r="O36">
-        <v>0.45425118394549763</v>
+        <v>0.4515160552941572</v>
       </c>
       <c r="P36">
-        <v>0.51376469156560867</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.5089224217314907</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>6.691033427421092E-2</v>
+        <v>0.06712372035595555</v>
       </c>
       <c r="C37">
-        <v>0.12995546307879799</v>
+        <v>0.1272070966638671</v>
       </c>
       <c r="D37">
-        <v>0.22560001767655291</v>
+        <v>0.2208118833581632</v>
       </c>
       <c r="E37">
-        <v>0.21530017061204021</v>
+        <v>0.2114662720038405</v>
       </c>
       <c r="F37">
-        <v>0.20166239399532521</v>
+        <v>0.1933223498168175</v>
       </c>
       <c r="G37">
-        <v>0.21235773332150309</v>
+        <v>0.2114115948780264</v>
       </c>
       <c r="H37">
-        <v>0.40746308083982541</v>
+        <v>0.3979938204352155</v>
       </c>
       <c r="I37">
-        <v>0.40188661105636669</v>
+        <v>0.3951815105900818</v>
       </c>
       <c r="J37">
-        <v>0.3868080659145125</v>
+        <v>0.38562907164682</v>
       </c>
       <c r="K37">
-        <v>0.35685411563574032</v>
+        <v>0.3548210150440563</v>
       </c>
       <c r="L37">
-        <v>0.35662746848163418</v>
+        <v>0.3541082907230997</v>
       </c>
       <c r="M37">
-        <v>0.34915170142931851</v>
+        <v>0.3500119236604545</v>
       </c>
       <c r="N37">
-        <v>0.39897839410742758</v>
+        <v>0.3972751460511397</v>
       </c>
       <c r="O37">
-        <v>0.44188287275028248</v>
+        <v>0.4418152621044252</v>
       </c>
       <c r="P37">
-        <v>0.50147505373625756</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.500030138326546</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>7.3801927335644696E-2</v>
+        <v>0.07097459395452993</v>
       </c>
       <c r="C38">
-        <v>0.14063093579723679</v>
+        <v>0.1341346374750732</v>
       </c>
       <c r="D38">
-        <v>0.2403838090116277</v>
+        <v>0.2276582597694148</v>
       </c>
       <c r="E38">
-        <v>0.2213718247595842</v>
+        <v>0.2080613621289629</v>
       </c>
       <c r="F38">
-        <v>0.20729454198602809</v>
+        <v>0.1940232340712603</v>
       </c>
       <c r="G38">
-        <v>0.2178238661956696</v>
+        <v>0.2046894891542711</v>
       </c>
       <c r="H38">
-        <v>0.39966576078240462</v>
+        <v>0.3786249718048775</v>
       </c>
       <c r="I38">
-        <v>0.38701467680610019</v>
+        <v>0.3808828426920138</v>
       </c>
       <c r="J38">
-        <v>0.37765370114345409</v>
+        <v>0.3697840949454629</v>
       </c>
       <c r="K38">
-        <v>0.35513496928044958</v>
+        <v>0.3495308207269456</v>
       </c>
       <c r="L38">
-        <v>0.35244927084462629</v>
+        <v>0.3489075195046826</v>
       </c>
       <c r="M38">
-        <v>0.34630533580615952</v>
+        <v>0.3467535350345985</v>
       </c>
       <c r="N38">
-        <v>0.3907044596731285</v>
+        <v>0.3840979831199897</v>
       </c>
       <c r="O38">
-        <v>0.43170234719041511</v>
+        <v>0.4135188558521105</v>
       </c>
       <c r="P38">
-        <v>0.47651475445729619</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.4693175063139187</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>7.1508773801562786E-2</v>
+        <v>0.07312781216885936</v>
       </c>
       <c r="C39">
-        <v>0.1383612960744027</v>
+        <v>0.1385980379417398</v>
       </c>
       <c r="D39">
-        <v>0.23827064262618669</v>
+        <v>0.2324817490564553</v>
       </c>
       <c r="E39">
-        <v>0.22312781879375079</v>
+        <v>0.2198006508246642</v>
       </c>
       <c r="F39">
-        <v>0.2113993080356554</v>
+        <v>0.2005136844959311</v>
       </c>
       <c r="G39">
-        <v>0.22069496467831271</v>
+        <v>0.2159977120725461</v>
       </c>
       <c r="H39">
-        <v>0.4031266625258238</v>
+        <v>0.3920246728198146</v>
       </c>
       <c r="I39">
-        <v>0.3969967055458089</v>
+        <v>0.3886624145198087</v>
       </c>
       <c r="J39">
-        <v>0.39194412426082142</v>
+        <v>0.3761863467946965</v>
       </c>
       <c r="K39">
-        <v>0.36932060375624698</v>
+        <v>0.3512552044744609</v>
       </c>
       <c r="L39">
-        <v>0.36449432421354472</v>
+        <v>0.3550666734474829</v>
       </c>
       <c r="M39">
-        <v>0.35953888437241072</v>
+        <v>0.3453046994587964</v>
       </c>
       <c r="N39">
-        <v>0.3883228337746969</v>
+        <v>0.3827495199269266</v>
       </c>
       <c r="O39">
-        <v>0.42156281146919988</v>
+        <v>0.4166101122363538</v>
       </c>
       <c r="P39">
-        <v>0.45949719779872039</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.4619329923383306</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>7.1246700151229095E-2</v>
+        <v>0.07259329892980523</v>
       </c>
       <c r="C40">
-        <v>0.1397961682858794</v>
+        <v>0.1345921176015186</v>
       </c>
       <c r="D40">
-        <v>0.23538584370792109</v>
+        <v>0.224968976087299</v>
       </c>
       <c r="E40">
-        <v>0.2189172453975651</v>
+        <v>0.210736283312182</v>
       </c>
       <c r="F40">
-        <v>0.20359566526071241</v>
+        <v>0.1988677515589791</v>
       </c>
       <c r="G40">
-        <v>0.2096641850149939</v>
+        <v>0.2101804318076823</v>
       </c>
       <c r="H40">
-        <v>0.3482792011699023</v>
+        <v>0.3568091301924498</v>
       </c>
       <c r="I40">
-        <v>0.3641032810443795</v>
+        <v>0.3678346252985997</v>
       </c>
       <c r="J40">
-        <v>0.3657883616179694</v>
+        <v>0.3650958239194341</v>
       </c>
       <c r="K40">
-        <v>0.31959747594907628</v>
+        <v>0.3101493435757393</v>
       </c>
       <c r="L40">
-        <v>0.33190228945069522</v>
+        <v>0.3245309266150806</v>
       </c>
       <c r="M40">
-        <v>0.33868886188899922</v>
+        <v>0.3207938442842869</v>
       </c>
       <c r="N40">
-        <v>0.36249163841162307</v>
+        <v>0.3450453601060295</v>
       </c>
       <c r="O40">
-        <v>0.38793406457663099</v>
+        <v>0.3775586785898579</v>
       </c>
       <c r="P40">
-        <v>0.4019126141042077</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.3885501509408991</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.14815827740035861</v>
+        <v>0.1490655056232215</v>
       </c>
       <c r="C41">
-        <v>0.32516363901309081</v>
+        <v>0.3365963060440385</v>
       </c>
       <c r="D41">
-        <v>0.2829993392269759</v>
+        <v>0.2970372341995523</v>
       </c>
       <c r="E41">
-        <v>0.32111822939922868</v>
+        <v>0.3247669300079283</v>
       </c>
       <c r="F41">
-        <v>0.5229156247426503</v>
+        <v>0.529167099466423</v>
       </c>
       <c r="G41">
-        <v>0.55201698526728127</v>
+        <v>0.5595924198457292</v>
       </c>
       <c r="H41">
-        <v>0.5554404383963949</v>
+        <v>0.5705356289432367</v>
       </c>
       <c r="I41">
-        <v>0.55451094140983426</v>
+        <v>0.5652848001488242</v>
       </c>
       <c r="J41">
-        <v>0.59984022537764559</v>
+        <v>0.6047920620891053</v>
       </c>
       <c r="K41">
-        <v>0.66239865047900415</v>
+        <v>0.6569646051951773</v>
       </c>
       <c r="L41">
-        <v>0.71320455979867992</v>
+        <v>0.7122697319011302</v>
       </c>
       <c r="M41">
-        <v>0.78886814014374973</v>
+        <v>0.7821650892338845</v>
       </c>
       <c r="N41">
-        <v>0.79417632802139515</v>
+        <v>0.790638522678474</v>
       </c>
       <c r="O41">
-        <v>0.81251870899758882</v>
+        <v>0.8058037141067239</v>
       </c>
       <c r="P41">
-        <v>0.82507049178823788</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.8168459668839659</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>9.7660723948482325E-2</v>
+        <v>0.09514104987411152</v>
       </c>
       <c r="C42">
-        <v>0.25233157488214109</v>
+        <v>0.2447027264272521</v>
       </c>
       <c r="D42">
-        <v>0.25457330807373663</v>
+        <v>0.2467679860347173</v>
       </c>
       <c r="E42">
-        <v>0.2875055467663612</v>
+        <v>0.2753739660144459</v>
       </c>
       <c r="F42">
-        <v>0.46648125261366369</v>
+        <v>0.4583491440772377</v>
       </c>
       <c r="G42">
-        <v>0.36098303127919601</v>
+        <v>0.3594137291615069</v>
       </c>
       <c r="H42">
-        <v>0.26639136809376462</v>
+        <v>0.2799617608452065</v>
       </c>
       <c r="I42">
-        <v>0.32579888457418948</v>
+        <v>0.3318537540065944</v>
       </c>
       <c r="J42">
-        <v>0.39961354807741628</v>
+        <v>0.4038340993871229</v>
       </c>
       <c r="K42">
-        <v>0.47139547386128361</v>
+        <v>0.4780321290321684</v>
       </c>
       <c r="L42">
-        <v>0.51810939454781424</v>
+        <v>0.5281896288282524</v>
       </c>
       <c r="M42">
-        <v>0.56413807465634647</v>
+        <v>0.5710940168667762</v>
       </c>
       <c r="N42">
-        <v>0.59140633238632279</v>
+        <v>0.6073802445048522</v>
       </c>
       <c r="O42">
-        <v>0.61397405548023865</v>
+        <v>0.6281179758646911</v>
       </c>
       <c r="P42">
-        <v>0.62788490853474332</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.6393305965373263</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>9.4213752516097746E-2</v>
+        <v>0.09822444421045938</v>
       </c>
       <c r="C43">
-        <v>0.22923560835051621</v>
+        <v>0.2271004104326133</v>
       </c>
       <c r="D43">
-        <v>0.22203017013221071</v>
+        <v>0.2171616570198887</v>
       </c>
       <c r="E43">
-        <v>0.21706479392622469</v>
+        <v>0.2235192977387296</v>
       </c>
       <c r="F43">
-        <v>0.34494375721018777</v>
+        <v>0.3460470624203866</v>
       </c>
       <c r="G43">
-        <v>0.28271731818733808</v>
+        <v>0.2839446117292471</v>
       </c>
       <c r="H43">
-        <v>0.25847895640205698</v>
+        <v>0.2584892996416455</v>
       </c>
       <c r="I43">
-        <v>0.30688606098349841</v>
+        <v>0.3064118626029327</v>
       </c>
       <c r="J43">
-        <v>0.35390790885726831</v>
+        <v>0.3584702385853312</v>
       </c>
       <c r="K43">
-        <v>0.3771408005191364</v>
+        <v>0.3875597346435117</v>
       </c>
       <c r="L43">
-        <v>0.43628439365746391</v>
+        <v>0.4343642889962925</v>
       </c>
       <c r="M43">
-        <v>0.43842184100221182</v>
+        <v>0.4449166534126943</v>
       </c>
       <c r="N43">
-        <v>0.50324548032728833</v>
+        <v>0.502602982482803</v>
       </c>
       <c r="O43">
-        <v>0.55582071584704074</v>
+        <v>0.554991258481824</v>
       </c>
       <c r="P43">
-        <v>0.59501239504910453</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.5851018650879898</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>0.14066009976491789</v>
+        <v>0.1429191901859554</v>
       </c>
       <c r="C44">
-        <v>0.13380456166095789</v>
+        <v>0.1382917768582791</v>
       </c>
       <c r="D44">
-        <v>0.19616677056514581</v>
+        <v>0.1978290497321425</v>
       </c>
       <c r="E44">
-        <v>0.26764308749374699</v>
+        <v>0.2684406729439894</v>
       </c>
       <c r="F44">
-        <v>0.36447226776952157</v>
+        <v>0.3693640016875881</v>
       </c>
       <c r="G44">
-        <v>0.38599786219165921</v>
+        <v>0.3740444685379316</v>
       </c>
       <c r="H44">
-        <v>0.4505769141644459</v>
+        <v>0.4506567953429675</v>
       </c>
       <c r="I44">
-        <v>0.54536574496431689</v>
+        <v>0.5476639537084137</v>
       </c>
       <c r="J44">
-        <v>0.61302276358953423</v>
+        <v>0.6118992102428739</v>
       </c>
       <c r="K44">
-        <v>0.62427535931713174</v>
+        <v>0.625927181603734</v>
       </c>
       <c r="L44">
-        <v>0.65481975942484416</v>
+        <v>0.658171421114172</v>
       </c>
       <c r="M44">
-        <v>0.66097797901557342</v>
+        <v>0.6650683833284702</v>
       </c>
       <c r="N44">
-        <v>0.70285963010362118</v>
+        <v>0.7042118087948535</v>
       </c>
       <c r="O44">
-        <v>0.75284707103634096</v>
+        <v>0.7502404264802125</v>
       </c>
       <c r="P44">
-        <v>0.83378070509167446</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.8240497012345671</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>0.16817861379341811</v>
+        <v>0.1705025651057053</v>
       </c>
       <c r="C45">
-        <v>0.49395242537340772</v>
+        <v>0.5079261556435932</v>
       </c>
       <c r="D45">
-        <v>0.48894696437298618</v>
+        <v>0.497343947703733</v>
       </c>
       <c r="E45">
-        <v>0.58407254467066383</v>
+        <v>0.5828731884114324</v>
       </c>
       <c r="F45">
-        <v>0.61783182645890644</v>
+        <v>0.6204915893506289</v>
       </c>
       <c r="G45">
-        <v>0.64734761547752173</v>
+        <v>0.6480264947355574</v>
       </c>
       <c r="H45">
-        <v>0.68977078706007777</v>
+        <v>0.6930919175501906</v>
       </c>
       <c r="I45">
-        <v>0.69281649026412762</v>
+        <v>0.6965361541665379</v>
       </c>
       <c r="J45">
-        <v>0.76053544198001977</v>
+        <v>0.7560593751624461</v>
       </c>
       <c r="K45">
-        <v>0.8201923551912117</v>
+        <v>0.8206776079059647</v>
       </c>
       <c r="L45">
-        <v>0.86263461817265741</v>
+        <v>0.8518367692122908</v>
       </c>
       <c r="M45">
-        <v>0.9215568257891299</v>
+        <v>0.9130858772949257</v>
       </c>
       <c r="N45">
-        <v>1.000528753028717</v>
+        <v>0.9922935037552721</v>
       </c>
       <c r="O45">
-        <v>1.029234594475219</v>
+        <v>1.022746503372373</v>
       </c>
       <c r="P45">
-        <v>1.063425625518817</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>1.063017939789391</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>5.7024109743938331E-2</v>
+        <v>0.05785073043397995</v>
       </c>
       <c r="C46">
-        <v>0.6036741609765125</v>
+        <v>0.6065384398387014</v>
       </c>
       <c r="D46">
-        <v>0.53148689394168414</v>
+        <v>0.5337321706532545</v>
       </c>
       <c r="E46">
-        <v>0.42508814098898029</v>
+        <v>0.4140207501100424</v>
       </c>
       <c r="F46">
-        <v>0.4191209995030028</v>
+        <v>0.4127102312907327</v>
       </c>
       <c r="G46">
-        <v>0.43805676239928121</v>
+        <v>0.442262418765104</v>
       </c>
       <c r="H46">
-        <v>0.4193894438351663</v>
+        <v>0.4175135219742113</v>
       </c>
       <c r="I46">
-        <v>0.45048610883494411</v>
+        <v>0.4461747467248362</v>
       </c>
       <c r="J46">
-        <v>0.48989905477302509</v>
+        <v>0.4926270002130788</v>
       </c>
       <c r="K46">
-        <v>0.50494840164316113</v>
+        <v>0.5121428708115358</v>
       </c>
       <c r="L46">
-        <v>0.53490015873757502</v>
+        <v>0.5452009976370191</v>
       </c>
       <c r="M46">
-        <v>0.59883492757550583</v>
+        <v>0.6095662719269516</v>
       </c>
       <c r="N46">
-        <v>0.62497810898456629</v>
+        <v>0.6370916423768997</v>
       </c>
       <c r="O46">
-        <v>0.64062449633481333</v>
+        <v>0.6503788765778507</v>
       </c>
       <c r="P46">
-        <v>0.68023675843830755</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.6919394556755433</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>9.7840702018259215E-2</v>
+        <v>0.110541872057105</v>
       </c>
       <c r="C47">
-        <v>0.23557625739879409</v>
+        <v>0.2505289486349513</v>
       </c>
       <c r="D47">
-        <v>0.37379025137952099</v>
+        <v>0.3843532461328641</v>
       </c>
       <c r="E47">
-        <v>0.44847416601942081</v>
+        <v>0.4660579052871431</v>
       </c>
       <c r="F47">
-        <v>0.36088606970708431</v>
+        <v>0.3608401355829365</v>
       </c>
       <c r="G47">
-        <v>0.35957629853215101</v>
+        <v>0.3679600456349216</v>
       </c>
       <c r="H47">
-        <v>0.39819405247843093</v>
+        <v>0.39836150241081</v>
       </c>
       <c r="I47">
-        <v>0.44150195029650191</v>
+        <v>0.4492293443922828</v>
       </c>
       <c r="J47">
-        <v>0.53840403192282305</v>
+        <v>0.5439030485689027</v>
       </c>
       <c r="K47">
-        <v>0.54566799587032966</v>
+        <v>0.5503002294094866</v>
       </c>
       <c r="L47">
-        <v>0.56821469300490568</v>
+        <v>0.5779980109062857</v>
       </c>
       <c r="M47">
-        <v>0.59317112657457183</v>
+        <v>0.6056296989672671</v>
       </c>
       <c r="N47">
-        <v>0.63495831259740743</v>
+        <v>0.6486172670868845</v>
       </c>
       <c r="O47">
-        <v>0.66950679618122455</v>
+        <v>0.6798944894643667</v>
       </c>
       <c r="P47">
-        <v>0.70330666548565879</v>
+        <v>0.7187812332221581</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P18 B20:P47 B19:K19 M19:P19">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_diff.xlsx
@@ -1,21 +1,205 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV1_diff</t>
+  </si>
+  <si>
+    <t>LV2_diff</t>
+  </si>
+  <si>
+    <t>LV3_diff</t>
+  </si>
+  <si>
+    <t>LV4_diff</t>
+  </si>
+  <si>
+    <t>LV5_diff</t>
+  </si>
+  <si>
+    <t>LV6_diff</t>
+  </si>
+  <si>
+    <t>LV7_diff</t>
+  </si>
+  <si>
+    <t>LV8_diff</t>
+  </si>
+  <si>
+    <t>LV9_diff</t>
+  </si>
+  <si>
+    <t>LV10_diff</t>
+  </si>
+  <si>
+    <t>LV11_diff</t>
+  </si>
+  <si>
+    <t>LV12_diff</t>
+  </si>
+  <si>
+    <t>LV13_diff</t>
+  </si>
+  <si>
+    <t>LV14_diff</t>
+  </si>
+  <si>
+    <t>LV15_diff</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +245,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +332,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +364,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +399,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +575,2173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_diff</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_diff</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_diff</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_diff</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_diff</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_diff</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_diff</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_diff</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_diff</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_diff</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_diff</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_diff</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_diff</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_diff</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>0.05563109121187663</v>
+        <v>5.3483345018787688E-2</v>
       </c>
       <c r="C2">
-        <v>0.1141681418988816</v>
+        <v>0.1109334815442696</v>
       </c>
       <c r="D2">
-        <v>0.1350444710473836</v>
+        <v>0.1275626526162906</v>
       </c>
       <c r="E2">
-        <v>0.1349674012921786</v>
+        <v>0.1296510764576137</v>
       </c>
       <c r="F2">
-        <v>0.1884064406164</v>
+        <v>0.18519184161256261</v>
       </c>
       <c r="G2">
-        <v>0.2713196956808726</v>
+        <v>0.26052142829382441</v>
       </c>
       <c r="H2">
-        <v>0.2592310812832144</v>
+        <v>0.25858561323823143</v>
       </c>
       <c r="I2">
-        <v>0.2956790093407661</v>
+        <v>0.30188221122903908</v>
       </c>
       <c r="J2">
-        <v>0.3886617813446304</v>
+        <v>0.38971266769634971</v>
       </c>
       <c r="K2">
-        <v>0.3838680453386868</v>
+        <v>0.37694762901717971</v>
       </c>
       <c r="L2">
-        <v>0.4192172857718998</v>
+        <v>0.4116603654905947</v>
       </c>
       <c r="M2">
-        <v>0.448640543181818</v>
+        <v>0.44557119940844492</v>
       </c>
       <c r="N2">
-        <v>0.438823116296887</v>
+        <v>0.43036962077203478</v>
       </c>
       <c r="O2">
-        <v>0.4247954252031471</v>
+        <v>0.42127416198012718</v>
       </c>
       <c r="P2">
-        <v>0.408770177648495</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.40439843433689071</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>0.05690719771576777</v>
+        <v>5.5302125896169077E-2</v>
       </c>
       <c r="C3">
-        <v>0.3656741634320526</v>
+        <v>0.3488141587862813</v>
       </c>
       <c r="D3">
-        <v>0.434426339568427</v>
+        <v>0.43159157081511978</v>
       </c>
       <c r="E3">
-        <v>0.3389676181624753</v>
+        <v>0.32808635100040362</v>
       </c>
       <c r="F3">
-        <v>0.3329328258166039</v>
+        <v>0.32969522063897022</v>
       </c>
       <c r="G3">
-        <v>0.3452363838127658</v>
+        <v>0.34667292276778572</v>
       </c>
       <c r="H3">
-        <v>0.3828228131874102</v>
+        <v>0.38020491519432709</v>
       </c>
       <c r="I3">
-        <v>0.413622321528216</v>
+        <v>0.41366323030280461</v>
       </c>
       <c r="J3">
-        <v>0.4145014783204052</v>
+        <v>0.42063371622703938</v>
       </c>
       <c r="K3">
-        <v>0.4224512782347168</v>
+        <v>0.41825700786014153</v>
       </c>
       <c r="L3">
-        <v>0.4517401422586612</v>
+        <v>0.44943925740747021</v>
       </c>
       <c r="M3">
-        <v>0.4918428870492673</v>
+        <v>0.48656629548309172</v>
       </c>
       <c r="N3">
-        <v>0.55513267396483</v>
+        <v>0.54373651912790388</v>
       </c>
       <c r="O3">
-        <v>0.6050636996151985</v>
+        <v>0.59595744633086722</v>
       </c>
       <c r="P3">
-        <v>0.6049074430458261</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.59721132819741851</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>0.0449421836207276</v>
+        <v>4.7646709791184648E-2</v>
       </c>
       <c r="C4">
-        <v>0.0668850110321679</v>
+        <v>7.5920221033311336E-2</v>
       </c>
       <c r="D4">
-        <v>0.1659928894240691</v>
+        <v>0.171384315270497</v>
       </c>
       <c r="E4">
-        <v>0.1783569362423504</v>
+        <v>0.18896773530942851</v>
       </c>
       <c r="F4">
-        <v>0.3420239290087844</v>
+        <v>0.35627912504691728</v>
       </c>
       <c r="G4">
-        <v>0.3166177519659896</v>
+        <v>0.32286720485019249</v>
       </c>
       <c r="H4">
-        <v>0.2856403152025805</v>
+        <v>0.29939590814054728</v>
       </c>
       <c r="I4">
-        <v>0.3525720787937667</v>
+        <v>0.36537451652651298</v>
       </c>
       <c r="J4">
-        <v>0.4000416086038752</v>
+        <v>0.40854357992663398</v>
       </c>
       <c r="K4">
-        <v>0.4349110002657961</v>
+        <v>0.43611262086831609</v>
       </c>
       <c r="L4">
-        <v>0.4424470332483899</v>
+        <v>0.44279253105856531</v>
       </c>
       <c r="M4">
-        <v>0.437228718338428</v>
+        <v>0.44039804177343161</v>
       </c>
       <c r="N4">
-        <v>0.4407208696816086</v>
+        <v>0.44365202158862471</v>
       </c>
       <c r="O4">
-        <v>0.4540594255382673</v>
+        <v>0.45637717666488298</v>
       </c>
       <c r="P4">
-        <v>0.4903302276268756</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.49811364121054719</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>0.04254617768974436</v>
+        <v>4.6309570625609718E-2</v>
       </c>
       <c r="C5">
-        <v>0.1699115880435274</v>
+        <v>0.16730704237347879</v>
       </c>
       <c r="D5">
-        <v>0.2071950525689907</v>
+        <v>0.21035163694963319</v>
       </c>
       <c r="E5">
-        <v>0.4538816264250834</v>
+        <v>0.45304789587920308</v>
       </c>
       <c r="F5">
-        <v>0.3262911013825802</v>
+        <v>0.31628510938599019</v>
       </c>
       <c r="G5">
-        <v>0.3832365990517081</v>
+        <v>0.38525536390628973</v>
       </c>
       <c r="H5">
-        <v>0.3972745928875172</v>
+        <v>0.38031282463972399</v>
       </c>
       <c r="I5">
-        <v>0.394553167573711</v>
+        <v>0.37698903418431279</v>
       </c>
       <c r="J5">
-        <v>0.356258973089829</v>
+        <v>0.34597106061792388</v>
       </c>
       <c r="K5">
-        <v>0.3555555621927972</v>
+        <v>0.34750133710701708</v>
       </c>
       <c r="L5">
-        <v>0.3702601460736324</v>
+        <v>0.3583163766079831</v>
       </c>
       <c r="M5">
-        <v>0.3944217102994207</v>
+        <v>0.37704324331716499</v>
       </c>
       <c r="N5">
-        <v>0.4473828481461682</v>
+        <v>0.4252044772058578</v>
       </c>
       <c r="O5">
-        <v>0.4849359986018648</v>
+        <v>0.46260796694169121</v>
       </c>
       <c r="P5">
-        <v>0.5325513475458843</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.50912391446051697</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>0.04764650509638872</v>
+        <v>3.9850279761545662E-2</v>
       </c>
       <c r="C6">
-        <v>0.1832078826317479</v>
+        <v>0.18366614109936871</v>
       </c>
       <c r="D6">
-        <v>0.186629706039013</v>
+        <v>0.19508236352047131</v>
       </c>
       <c r="E6">
-        <v>0.4429769980657507</v>
+        <v>0.45130723937544881</v>
       </c>
       <c r="F6">
-        <v>0.2842376428696332</v>
+        <v>0.30016566897396513</v>
       </c>
       <c r="G6">
-        <v>0.3224976662723964</v>
+        <v>0.33154342473381188</v>
       </c>
       <c r="H6">
-        <v>0.3192029394550427</v>
+        <v>0.33987839236988421</v>
       </c>
       <c r="I6">
-        <v>0.2792322794247858</v>
+        <v>0.28916847917522942</v>
       </c>
       <c r="J6">
-        <v>0.2807275689283303</v>
+        <v>0.29456669091213972</v>
       </c>
       <c r="K6">
-        <v>0.2906071650731401</v>
+        <v>0.30537809723068809</v>
       </c>
       <c r="L6">
-        <v>0.3118124417371679</v>
+        <v>0.32632404273344368</v>
       </c>
       <c r="M6">
-        <v>0.3383141829451914</v>
+        <v>0.34659729441113879</v>
       </c>
       <c r="N6">
-        <v>0.3699205888631</v>
+        <v>0.37605952326493369</v>
       </c>
       <c r="O6">
-        <v>0.3839209928119195</v>
+        <v>0.38837597870062729</v>
       </c>
       <c r="P6">
-        <v>0.4290510674750357</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.43671193494030708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>0.05129048607482597</v>
+        <v>5.0372378653645911E-2</v>
       </c>
       <c r="C7">
-        <v>0.08026916604620872</v>
+        <v>8.3156509790031044E-2</v>
       </c>
       <c r="D7">
-        <v>0.162238012111606</v>
+        <v>0.16885009569240161</v>
       </c>
       <c r="E7">
-        <v>0.204877658112701</v>
+        <v>0.20914476738433449</v>
       </c>
       <c r="F7">
-        <v>0.3265856479808826</v>
+        <v>0.33281379900149932</v>
       </c>
       <c r="G7">
-        <v>0.3756123723689413</v>
+        <v>0.38005379572348652</v>
       </c>
       <c r="H7">
-        <v>0.3348907868581779</v>
+        <v>0.34983876839534989</v>
       </c>
       <c r="I7">
-        <v>0.3017558244949129</v>
+        <v>0.30936124694395251</v>
       </c>
       <c r="J7">
-        <v>0.3701208929894777</v>
+        <v>0.38962522734039612</v>
       </c>
       <c r="K7">
-        <v>0.4095258209927922</v>
+        <v>0.42052712927109948</v>
       </c>
       <c r="L7">
-        <v>0.4476402903214161</v>
+        <v>0.44051994130482103</v>
       </c>
       <c r="M7">
-        <v>0.4678828626805819</v>
+        <v>0.45935917567577439</v>
       </c>
       <c r="N7">
-        <v>0.4359159498800386</v>
+        <v>0.42370965949408002</v>
       </c>
       <c r="O7">
-        <v>0.4430143221153212</v>
+        <v>0.43244862428016051</v>
       </c>
       <c r="P7">
-        <v>0.4633799388125079</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.45448271023067571</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>0.04470175764369694</v>
+        <v>4.5950672964934873E-2</v>
       </c>
       <c r="C8">
-        <v>0.07694034708910516</v>
+        <v>8.0160221473292742E-2</v>
       </c>
       <c r="D8">
-        <v>0.174302974153233</v>
+        <v>0.17050009299828739</v>
       </c>
       <c r="E8">
-        <v>0.3311319338950985</v>
+        <v>0.32170118667197939</v>
       </c>
       <c r="F8">
-        <v>0.3175909284541057</v>
+        <v>0.32714445394571479</v>
       </c>
       <c r="G8">
-        <v>0.2896807797711416</v>
+        <v>0.29281384454727338</v>
       </c>
       <c r="H8">
-        <v>0.3288111436757092</v>
+        <v>0.33548198337673368</v>
       </c>
       <c r="I8">
-        <v>0.3477562568975899</v>
+        <v>0.35316639296204527</v>
       </c>
       <c r="J8">
-        <v>0.3606248465013538</v>
+        <v>0.36158671762014621</v>
       </c>
       <c r="K8">
-        <v>0.3772489238440928</v>
+        <v>0.37682348709146513</v>
       </c>
       <c r="L8">
-        <v>0.3966809285322576</v>
+        <v>0.40641576739809671</v>
       </c>
       <c r="M8">
-        <v>0.3934641598669178</v>
+        <v>0.40118914505849662</v>
       </c>
       <c r="N8">
-        <v>0.3885272226696631</v>
+        <v>0.40165868274306887</v>
       </c>
       <c r="O8">
-        <v>0.4049596406593581</v>
+        <v>0.41665500591088361</v>
       </c>
       <c r="P8">
-        <v>0.4399850292092317</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.44875613451379331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0.03913827910869518</v>
+        <v>4.3598446448248007E-2</v>
       </c>
       <c r="C9">
-        <v>0.07235782064911438</v>
+        <v>7.5067672206909103E-2</v>
       </c>
       <c r="D9">
-        <v>0.1636434530230356</v>
+        <v>0.1724259506333877</v>
       </c>
       <c r="E9">
-        <v>0.2864773018512722</v>
+        <v>0.30178660790726541</v>
       </c>
       <c r="F9">
-        <v>0.2830164762182684</v>
+        <v>0.29267016642401072</v>
       </c>
       <c r="G9">
-        <v>0.2420818136605645</v>
+        <v>0.25013111766638829</v>
       </c>
       <c r="H9">
-        <v>0.2683509765283729</v>
+        <v>0.28616463670316422</v>
       </c>
       <c r="I9">
-        <v>0.2722841378063342</v>
+        <v>0.28236317443110831</v>
       </c>
       <c r="J9">
-        <v>0.2756746887423167</v>
+        <v>0.28937062762100663</v>
       </c>
       <c r="K9">
-        <v>0.2809646024966752</v>
+        <v>0.29170859324146248</v>
       </c>
       <c r="L9">
-        <v>0.3167418973636869</v>
+        <v>0.33336029264523109</v>
       </c>
       <c r="M9">
-        <v>0.2888206484321051</v>
+        <v>0.309613783764013</v>
       </c>
       <c r="N9">
-        <v>0.2908494111471236</v>
+        <v>0.3115794753527763</v>
       </c>
       <c r="O9">
-        <v>0.3076989625299678</v>
+        <v>0.31960019740103318</v>
       </c>
       <c r="P9">
-        <v>0.3277006448445615</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.33976628124955538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>0.04742784847370712</v>
+        <v>4.1877415907953887E-2</v>
       </c>
       <c r="C10">
-        <v>0.07592970546860937</v>
+        <v>7.0595506763611524E-2</v>
       </c>
       <c r="D10">
-        <v>0.1655611608253206</v>
+        <v>0.15894140410374949</v>
       </c>
       <c r="E10">
-        <v>0.2965147460019965</v>
+        <v>0.278140953553774</v>
       </c>
       <c r="F10">
-        <v>0.28863988315657</v>
+        <v>0.27621022214855889</v>
       </c>
       <c r="G10">
-        <v>0.2536556769020608</v>
+        <v>0.23691337791987921</v>
       </c>
       <c r="H10">
-        <v>0.2717997133197901</v>
+        <v>0.26344504467297247</v>
       </c>
       <c r="I10">
-        <v>0.2793942038953015</v>
+        <v>0.26839805831534502</v>
       </c>
       <c r="J10">
-        <v>0.2858822708258912</v>
+        <v>0.27515869559963141</v>
       </c>
       <c r="K10">
-        <v>0.2752615182132011</v>
+        <v>0.28190437710658772</v>
       </c>
       <c r="L10">
-        <v>0.3264273006355155</v>
+        <v>0.32050459944951137</v>
       </c>
       <c r="M10">
-        <v>0.295086384720621</v>
+        <v>0.29038879491035879</v>
       </c>
       <c r="N10">
-        <v>0.2905058778256577</v>
+        <v>0.29398226991595011</v>
       </c>
       <c r="O10">
-        <v>0.3117439654784756</v>
+        <v>0.31136655366391869</v>
       </c>
       <c r="P10">
-        <v>0.3274816490644558</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.33470840656863288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>0.04276718134545309</v>
+        <v>4.6738063074199282E-2</v>
       </c>
       <c r="C11">
-        <v>0.07648880988659185</v>
+        <v>7.6678040525676575E-2</v>
       </c>
       <c r="D11">
-        <v>0.1720536324294984</v>
+        <v>0.16771446279671451</v>
       </c>
       <c r="E11">
-        <v>0.3049550503545098</v>
+        <v>0.29700889794512642</v>
       </c>
       <c r="F11">
-        <v>0.2969331527739561</v>
+        <v>0.28981885812985508</v>
       </c>
       <c r="G11">
-        <v>0.2473660309123886</v>
+        <v>0.25779627006099298</v>
       </c>
       <c r="H11">
-        <v>0.2831893855415532</v>
+        <v>0.29229700772365541</v>
       </c>
       <c r="I11">
-        <v>0.2798800743463626</v>
+        <v>0.30024946168438199</v>
       </c>
       <c r="J11">
-        <v>0.2855788937798665</v>
+        <v>0.30555430255547661</v>
       </c>
       <c r="K11">
-        <v>0.2809568941021485</v>
+        <v>0.29542736393401758</v>
       </c>
       <c r="L11">
-        <v>0.3117011848275796</v>
+        <v>0.32532606672946229</v>
       </c>
       <c r="M11">
-        <v>0.2921491830835297</v>
+        <v>0.30487817911518272</v>
       </c>
       <c r="N11">
-        <v>0.2926963067577533</v>
+        <v>0.30406577728503942</v>
       </c>
       <c r="O11">
-        <v>0.3147100788722646</v>
+        <v>0.32390403897306702</v>
       </c>
       <c r="P11">
-        <v>0.3288105997358367</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.33236476004080662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>0.0444761913439795</v>
+        <v>4.2543650516439158E-2</v>
       </c>
       <c r="C12">
-        <v>0.1700666437450545</v>
+        <v>0.1547330652668534</v>
       </c>
       <c r="D12">
-        <v>0.2066130032248917</v>
+        <v>0.20426911637204689</v>
       </c>
       <c r="E12">
-        <v>0.4160587768563994</v>
+        <v>0.39814031567535818</v>
       </c>
       <c r="F12">
-        <v>0.3663780309195002</v>
+        <v>0.36338141114878852</v>
       </c>
       <c r="G12">
-        <v>0.444160183451998</v>
+        <v>0.44357095315044442</v>
       </c>
       <c r="H12">
-        <v>0.3721502157690779</v>
+        <v>0.37743903330138101</v>
       </c>
       <c r="I12">
-        <v>0.3329580972267032</v>
+        <v>0.34930802840884612</v>
       </c>
       <c r="J12">
-        <v>0.3090886126920657</v>
+        <v>0.3250177759616652</v>
       </c>
       <c r="K12">
-        <v>0.3063301053317428</v>
+        <v>0.32373156207134002</v>
       </c>
       <c r="L12">
-        <v>0.3177318220026226</v>
+        <v>0.33668262285562289</v>
       </c>
       <c r="M12">
-        <v>0.3338393672699034</v>
+        <v>0.35095642164934171</v>
       </c>
       <c r="N12">
-        <v>0.3741825266275229</v>
+        <v>0.39277807210170251</v>
       </c>
       <c r="O12">
-        <v>0.4089364514923131</v>
+        <v>0.42272801174032892</v>
       </c>
       <c r="P12">
-        <v>0.4703620992886053</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.48601230573187171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>0.06261050216397603</v>
+        <v>5.7761211552443362E-2</v>
       </c>
       <c r="C13">
-        <v>0.2975907519866996</v>
+        <v>0.28984712988970768</v>
       </c>
       <c r="D13">
-        <v>0.2877311587416513</v>
+        <v>0.29244237750647489</v>
       </c>
       <c r="E13">
-        <v>0.4421020998829689</v>
+        <v>0.44031664980542251</v>
       </c>
       <c r="F13">
-        <v>0.4807896205755515</v>
+        <v>0.48722725336027062</v>
       </c>
       <c r="G13">
-        <v>0.458787874669663</v>
+        <v>0.46386330428498479</v>
       </c>
       <c r="H13">
-        <v>0.5453248621813724</v>
+        <v>0.5444378937859683</v>
       </c>
       <c r="I13">
-        <v>0.5516678025065402</v>
+        <v>0.55065138217385701</v>
       </c>
       <c r="J13">
-        <v>0.5438808607845341</v>
+        <v>0.53449370393197015</v>
       </c>
       <c r="K13">
-        <v>0.5147783048545214</v>
+        <v>0.50986941533696784</v>
       </c>
       <c r="L13">
-        <v>0.5273766197162724</v>
+        <v>0.5180871465599769</v>
       </c>
       <c r="M13">
-        <v>0.5395243343657288</v>
+        <v>0.52781042538132406</v>
       </c>
       <c r="N13">
-        <v>0.5459551209787161</v>
+        <v>0.53840379941134786</v>
       </c>
       <c r="O13">
-        <v>0.5496833579968312</v>
+        <v>0.53682564511574071</v>
       </c>
       <c r="P13">
-        <v>0.574481191049511</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.56482827519540346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>0.05027095809080804</v>
+        <v>4.7128445789057088E-2</v>
       </c>
       <c r="C14">
-        <v>0.07642322209012464</v>
+        <v>7.7045065425402445E-2</v>
       </c>
       <c r="D14">
-        <v>0.1555281913516285</v>
+        <v>0.15913184820237611</v>
       </c>
       <c r="E14">
-        <v>0.188744501300975</v>
+        <v>0.1995411591367888</v>
       </c>
       <c r="F14">
-        <v>0.3069170741815327</v>
+        <v>0.30952999189281849</v>
       </c>
       <c r="G14">
-        <v>0.3406115334704234</v>
+        <v>0.34398584231050328</v>
       </c>
       <c r="H14">
-        <v>0.3059682287476592</v>
+        <v>0.30937336008536992</v>
       </c>
       <c r="I14">
-        <v>0.2593974302832309</v>
+        <v>0.26571603303995539</v>
       </c>
       <c r="J14">
-        <v>0.3263866469108909</v>
+        <v>0.32154297030656331</v>
       </c>
       <c r="K14">
-        <v>0.3528932582879548</v>
+        <v>0.35817413196527692</v>
       </c>
       <c r="L14">
-        <v>0.3599363194579424</v>
+        <v>0.36106684639228009</v>
       </c>
       <c r="M14">
-        <v>0.3487565035053625</v>
+        <v>0.35576097841057253</v>
       </c>
       <c r="N14">
-        <v>0.3337412098676969</v>
+        <v>0.33342329976867202</v>
       </c>
       <c r="O14">
-        <v>0.3396956056816118</v>
+        <v>0.3405607169712655</v>
       </c>
       <c r="P14">
-        <v>0.3361246407791405</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.33981971886600681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>0.05392207774531405</v>
+        <v>4.381244659732568E-2</v>
       </c>
       <c r="C15">
-        <v>0.08037960362776039</v>
+        <v>7.2128339760264309E-2</v>
       </c>
       <c r="D15">
-        <v>0.1584588310902402</v>
+        <v>0.1478410592527484</v>
       </c>
       <c r="E15">
-        <v>0.1900384656425244</v>
+        <v>0.1783372894058029</v>
       </c>
       <c r="F15">
-        <v>0.3059757274329106</v>
+        <v>0.27830318683197369</v>
       </c>
       <c r="G15">
-        <v>0.3413622682736192</v>
+        <v>0.31514376975502439</v>
       </c>
       <c r="H15">
-        <v>0.2966005455390077</v>
+        <v>0.27638716882987258</v>
       </c>
       <c r="I15">
-        <v>0.2672207219621753</v>
+        <v>0.25250926202669383</v>
       </c>
       <c r="J15">
-        <v>0.3219843364678084</v>
+        <v>0.30323242205048961</v>
       </c>
       <c r="K15">
-        <v>0.3492516383106664</v>
+        <v>0.34842250963256433</v>
       </c>
       <c r="L15">
-        <v>0.3587061925465609</v>
+        <v>0.35934449275766023</v>
       </c>
       <c r="M15">
-        <v>0.3548177736867306</v>
+        <v>0.35348129499412317</v>
       </c>
       <c r="N15">
-        <v>0.3311109667694382</v>
+        <v>0.33155805393556692</v>
       </c>
       <c r="O15">
-        <v>0.3396110656482245</v>
+        <v>0.33930106199681798</v>
       </c>
       <c r="P15">
-        <v>0.3385779703350842</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.34299578606650533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>0.04664888461001218</v>
+        <v>5.0841634388884928E-2</v>
       </c>
       <c r="C16">
-        <v>0.07326891504712113</v>
+        <v>8.1749906124201951E-2</v>
       </c>
       <c r="D16">
-        <v>0.1521185827590552</v>
+        <v>0.15862121456403469</v>
       </c>
       <c r="E16">
-        <v>0.182514240441684</v>
+        <v>0.19103240731513119</v>
       </c>
       <c r="F16">
-        <v>0.290020099723902</v>
+        <v>0.29549242294921491</v>
       </c>
       <c r="G16">
-        <v>0.3365131760799982</v>
+        <v>0.32940429273386163</v>
       </c>
       <c r="H16">
-        <v>0.3047279497202996</v>
+        <v>0.28981839648012708</v>
       </c>
       <c r="I16">
-        <v>0.2571377862722082</v>
+        <v>0.24821799490493271</v>
       </c>
       <c r="J16">
-        <v>0.3051574331953158</v>
+        <v>0.30694326145122958</v>
       </c>
       <c r="K16">
-        <v>0.3417476173633764</v>
+        <v>0.34828654637431189</v>
       </c>
       <c r="L16">
-        <v>0.3595511662701078</v>
+        <v>0.36110500112010879</v>
       </c>
       <c r="M16">
-        <v>0.3522203621096303</v>
+        <v>0.35240069031375892</v>
       </c>
       <c r="N16">
-        <v>0.3240611020332523</v>
+        <v>0.32870167210206819</v>
       </c>
       <c r="O16">
-        <v>0.3249415704943839</v>
+        <v>0.33039174730935428</v>
       </c>
       <c r="P16">
-        <v>0.3297103471131173</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.33215084840556469</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0.0479064310087228</v>
+        <v>4.604856529385528E-2</v>
       </c>
       <c r="C17">
-        <v>0.07686522950475091</v>
+        <v>6.8922906674370552E-2</v>
       </c>
       <c r="D17">
-        <v>0.1576864453582562</v>
+        <v>0.1464982027046684</v>
       </c>
       <c r="E17">
-        <v>0.191013894355692</v>
+        <v>0.17780623504288781</v>
       </c>
       <c r="F17">
-        <v>0.289548863418194</v>
+        <v>0.28805711094005287</v>
       </c>
       <c r="G17">
-        <v>0.3366530547772575</v>
+        <v>0.32392789743008849</v>
       </c>
       <c r="H17">
-        <v>0.2971437442784969</v>
+        <v>0.29463112275101849</v>
       </c>
       <c r="I17">
-        <v>0.2458337094779826</v>
+        <v>0.26048453228532997</v>
       </c>
       <c r="J17">
-        <v>0.3042249333866945</v>
+        <v>0.29892013573100762</v>
       </c>
       <c r="K17">
-        <v>0.3464284633457698</v>
+        <v>0.34976222083550718</v>
       </c>
       <c r="L17">
-        <v>0.3671391756407908</v>
+        <v>0.36026733724195159</v>
       </c>
       <c r="M17">
-        <v>0.3521233180816134</v>
+        <v>0.34957738236934499</v>
       </c>
       <c r="N17">
-        <v>0.3436127231159531</v>
+        <v>0.33495716488869509</v>
       </c>
       <c r="O17">
-        <v>0.3500620387040659</v>
+        <v>0.34426101683197352</v>
       </c>
       <c r="P17">
-        <v>0.3533993865842958</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.33545999969046603</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>0.04304763026957641</v>
+        <v>4.4631846224815919E-2</v>
       </c>
       <c r="C18">
-        <v>0.1735714312457761</v>
+        <v>0.16626204059303809</v>
       </c>
       <c r="D18">
-        <v>0.2151166860059246</v>
+        <v>0.20882504556721479</v>
       </c>
       <c r="E18">
-        <v>0.433445309185141</v>
+        <v>0.42187966669483368</v>
       </c>
       <c r="F18">
-        <v>0.3318260239118914</v>
+        <v>0.33611048100747509</v>
       </c>
       <c r="G18">
-        <v>0.3939112472911001</v>
+        <v>0.40560330122882082</v>
       </c>
       <c r="H18">
-        <v>0.4380192541253982</v>
+        <v>0.44955328114654403</v>
       </c>
       <c r="I18">
-        <v>0.3757840428054818</v>
+        <v>0.38466774048748598</v>
       </c>
       <c r="J18">
-        <v>0.3272513172692609</v>
+        <v>0.33071469870306958</v>
       </c>
       <c r="K18">
-        <v>0.318185148433376</v>
+        <v>0.32517510689741952</v>
       </c>
       <c r="L18">
-        <v>0.340910048068931</v>
+        <v>0.34712908412936222</v>
       </c>
       <c r="M18">
-        <v>0.3532559724747233</v>
+        <v>0.36295299314470408</v>
       </c>
       <c r="N18">
-        <v>0.4072002027541484</v>
+        <v>0.41657610462921218</v>
       </c>
       <c r="O18">
-        <v>0.4520461519661561</v>
+        <v>0.45892686202326499</v>
       </c>
       <c r="P18">
-        <v>0.4940222878048771</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.50207700239185771</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>0.04417430208801205</v>
+        <v>5.2708975902415613E-2</v>
       </c>
       <c r="C19">
-        <v>0.1958710567660968</v>
+        <v>0.19710557021720779</v>
       </c>
       <c r="D19">
-        <v>0.2109897303077424</v>
+        <v>0.21232151785044509</v>
       </c>
       <c r="E19">
-        <v>0.4617027682871863</v>
+        <v>0.4476623946971352</v>
       </c>
       <c r="F19">
-        <v>0.3020456258756535</v>
+        <v>0.29778995709485362</v>
       </c>
       <c r="G19">
-        <v>0.3174250610331317</v>
+        <v>0.30966579726546878</v>
       </c>
       <c r="H19">
-        <v>0.2820043288851229</v>
+        <v>0.29052595681676557</v>
       </c>
       <c r="I19">
-        <v>0.2684348563767193</v>
+        <v>0.27290818776344788</v>
       </c>
       <c r="J19">
-        <v>0.2655374724131538</v>
+        <v>0.26582541878598182</v>
       </c>
       <c r="K19">
-        <v>0.2844623695912796</v>
+        <v>0.28484306209978838</v>
       </c>
       <c r="L19">
-        <v>0.3087968769426582</v>
+        <v>0.30517169705926189</v>
       </c>
       <c r="M19">
-        <v>0.3327964419287649</v>
+        <v>0.33473542947227591</v>
       </c>
       <c r="N19">
-        <v>0.3705356140094986</v>
+        <v>0.3773884746644558</v>
       </c>
       <c r="O19">
-        <v>0.381987476917319</v>
+        <v>0.38344733055633923</v>
       </c>
       <c r="P19">
-        <v>0.4193121638008005</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.41661820893305762</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
-        <v>0.04284921055280405</v>
+        <v>4.4485022521757893E-2</v>
       </c>
       <c r="C20">
-        <v>0.2339946617047225</v>
+        <v>0.23531330454122301</v>
       </c>
       <c r="D20">
-        <v>0.2269782832932367</v>
+        <v>0.22680532155186339</v>
       </c>
       <c r="E20">
-        <v>0.2584665591535685</v>
+        <v>0.25887628552903802</v>
       </c>
       <c r="F20">
-        <v>0.2541150575331637</v>
+        <v>0.24321915615810771</v>
       </c>
       <c r="G20">
-        <v>0.3376126165980769</v>
+        <v>0.31523910129096161</v>
       </c>
       <c r="H20">
-        <v>0.2911449608697473</v>
+        <v>0.26754444153885198</v>
       </c>
       <c r="I20">
-        <v>0.2821159710633154</v>
+        <v>0.26843646866376458</v>
       </c>
       <c r="J20">
-        <v>0.2662891773550174</v>
+        <v>0.25777983526003112</v>
       </c>
       <c r="K20">
-        <v>0.2895538165060705</v>
+        <v>0.27664016472779451</v>
       </c>
       <c r="L20">
-        <v>0.3160419586963638</v>
+        <v>0.30881278412936403</v>
       </c>
       <c r="M20">
-        <v>0.3502621071878617</v>
+        <v>0.34160731662558952</v>
       </c>
       <c r="N20">
-        <v>0.3307697432820608</v>
+        <v>0.32492157931961191</v>
       </c>
       <c r="O20">
-        <v>0.3531120088106151</v>
+        <v>0.34562641902032032</v>
       </c>
       <c r="P20">
-        <v>0.3743896187317931</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.36018100983053047</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>0.05653671480929612</v>
+        <v>5.7176475485445313E-2</v>
       </c>
       <c r="C21">
-        <v>0.338060457377255</v>
+        <v>0.34474415971313699</v>
       </c>
       <c r="D21">
-        <v>0.4042615311971539</v>
+        <v>0.40668686118984071</v>
       </c>
       <c r="E21">
-        <v>0.3335062605363162</v>
+        <v>0.3313433419076921</v>
       </c>
       <c r="F21">
-        <v>0.3326134881511972</v>
+        <v>0.32543181557040451</v>
       </c>
       <c r="G21">
-        <v>0.3752173042017648</v>
+        <v>0.36575660344129007</v>
       </c>
       <c r="H21">
-        <v>0.4292435262687698</v>
+        <v>0.42374609914788969</v>
       </c>
       <c r="I21">
-        <v>0.4609472623731069</v>
+        <v>0.44360566102029819</v>
       </c>
       <c r="J21">
-        <v>0.4328565958281419</v>
+        <v>0.42507917619999541</v>
       </c>
       <c r="K21">
-        <v>0.4434765708249784</v>
+        <v>0.43507926831507038</v>
       </c>
       <c r="L21">
-        <v>0.4595674181720639</v>
+        <v>0.4537754329631804</v>
       </c>
       <c r="M21">
-        <v>0.5028969284896094</v>
+        <v>0.49557340052158971</v>
       </c>
       <c r="N21">
-        <v>0.5656593334519245</v>
+        <v>0.56537977459443656</v>
       </c>
       <c r="O21">
-        <v>0.626010475226663</v>
+        <v>0.62750357631847886</v>
       </c>
       <c r="P21">
-        <v>0.6355569504279894</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.63491165835103869</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>0.05644391737128923</v>
+        <v>5.7797712280034608E-2</v>
       </c>
       <c r="C22">
-        <v>0.336553835544928</v>
+        <v>0.3374797893897219</v>
       </c>
       <c r="D22">
-        <v>0.3948563566249144</v>
+        <v>0.39646441032717428</v>
       </c>
       <c r="E22">
-        <v>0.308804025987394</v>
+        <v>0.31824179318065687</v>
       </c>
       <c r="F22">
-        <v>0.3147724370078923</v>
+        <v>0.3256039193335899</v>
       </c>
       <c r="G22">
-        <v>0.359405158993915</v>
+        <v>0.36379129549259148</v>
       </c>
       <c r="H22">
-        <v>0.4359646447975307</v>
+        <v>0.44394322547393472</v>
       </c>
       <c r="I22">
-        <v>0.4849489258923367</v>
+        <v>0.49173642863457162</v>
       </c>
       <c r="J22">
-        <v>0.4744710263679418</v>
+        <v>0.47595550657362629</v>
       </c>
       <c r="K22">
-        <v>0.4827262931210595</v>
+        <v>0.4834510796783828</v>
       </c>
       <c r="L22">
-        <v>0.5206850334384708</v>
+        <v>0.50807319067670553</v>
       </c>
       <c r="M22">
-        <v>0.5484138366106823</v>
+        <v>0.52960895991398527</v>
       </c>
       <c r="N22">
-        <v>0.6012456621385575</v>
+        <v>0.5815422034683303</v>
       </c>
       <c r="O22">
-        <v>0.6271378139626059</v>
+        <v>0.60869769659375494</v>
       </c>
       <c r="P22">
-        <v>0.6461711709746838</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.63116209553977898</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
       </c>
       <c r="B23">
-        <v>0.044867470039565</v>
+        <v>4.5568968474300683E-2</v>
       </c>
       <c r="C23">
-        <v>0.2622818540564527</v>
+        <v>0.26821987763124788</v>
       </c>
       <c r="D23">
-        <v>0.2650069795290621</v>
+        <v>0.27798319431056617</v>
       </c>
       <c r="E23">
-        <v>0.2181585693451353</v>
+        <v>0.21938204127657729</v>
       </c>
       <c r="F23">
-        <v>0.2884794746959232</v>
+        <v>0.29933849313399291</v>
       </c>
       <c r="G23">
-        <v>0.2833511991024186</v>
+        <v>0.29664545030764572</v>
       </c>
       <c r="H23">
-        <v>0.301482298919881</v>
+        <v>0.31621432057981907</v>
       </c>
       <c r="I23">
-        <v>0.3450827149249732</v>
+        <v>0.36350094291558771</v>
       </c>
       <c r="J23">
-        <v>0.3662614776156696</v>
+        <v>0.37906551879827549</v>
       </c>
       <c r="K23">
-        <v>0.431541371722604</v>
+        <v>0.43223481903895378</v>
       </c>
       <c r="L23">
-        <v>0.4677317180054811</v>
+        <v>0.46154661378231171</v>
       </c>
       <c r="M23">
-        <v>0.5297507855581582</v>
+        <v>0.51922050051765112</v>
       </c>
       <c r="N23">
-        <v>0.5515475809591415</v>
+        <v>0.54352307463788385</v>
       </c>
       <c r="O23">
-        <v>0.5687978068628967</v>
+        <v>0.55432636755310005</v>
       </c>
       <c r="P23">
-        <v>0.6024408876620548</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.59263478141691306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
       </c>
       <c r="B24">
-        <v>0.103410919829069</v>
+        <v>7.4267070811828664E-2</v>
       </c>
       <c r="C24">
-        <v>0.1469524185218946</v>
+        <v>0.14160141564911349</v>
       </c>
       <c r="D24">
-        <v>0.1977443190989291</v>
+        <v>0.23733973398086039</v>
       </c>
       <c r="E24">
-        <v>0.2964798032407697</v>
+        <v>0.22675186891591681</v>
       </c>
       <c r="F24">
-        <v>0.3894485419447791</v>
+        <v>0.24206948010612989</v>
       </c>
       <c r="G24">
-        <v>0.5807821546342696</v>
+        <v>0.2309171556696184</v>
       </c>
       <c r="H24">
-        <v>0.6054864430544087</v>
+        <v>0.31246212856997557</v>
       </c>
       <c r="I24">
-        <v>0.6949531437266794</v>
+        <v>0.45399965019281441</v>
       </c>
       <c r="J24">
-        <v>0.807396382918422</v>
+        <v>0.46809719399851729</v>
       </c>
       <c r="K24">
-        <v>1.008876905866965</v>
+        <v>0.46622042154120991</v>
       </c>
       <c r="L24">
-        <v>1.023589330527837</v>
+        <v>0.48589663231732189</v>
       </c>
       <c r="M24">
-        <v>1.099647301209441</v>
+        <v>0.57759922741166614</v>
       </c>
       <c r="N24">
-        <v>1.228509155281901</v>
+        <v>0.68995924555855814</v>
       </c>
       <c r="O24">
-        <v>1.331146139927539</v>
+        <v>0.77168659873424073</v>
       </c>
       <c r="P24">
-        <v>1.471373251064127</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.88198699821748461</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>39</v>
       </c>
       <c r="B25">
-        <v>0.2382746641053779</v>
+        <v>7.2073788732338329E-2</v>
       </c>
       <c r="C25">
-        <v>0.3444317422076331</v>
+        <v>0.13832325887405719</v>
       </c>
       <c r="D25">
-        <v>0.3954122272763885</v>
+        <v>0.24462476439274031</v>
       </c>
       <c r="E25">
-        <v>0.4093038213081669</v>
+        <v>0.23234720561222119</v>
       </c>
       <c r="F25">
-        <v>0.6148450878934525</v>
+        <v>0.2209559782618333</v>
       </c>
       <c r="G25">
-        <v>0.7367066031030418</v>
+        <v>0.25150924578447692</v>
       </c>
       <c r="H25">
-        <v>0.7900602188212056</v>
+        <v>0.54788789299357332</v>
       </c>
       <c r="I25">
-        <v>0.8153819312873282</v>
+        <v>0.53778368439452184</v>
       </c>
       <c r="J25">
-        <v>0.8842218272049923</v>
+        <v>0.51953921772633416</v>
       </c>
       <c r="K25">
-        <v>1.027560154489822</v>
+        <v>0.4957782752048695</v>
       </c>
       <c r="L25">
-        <v>1.114209500206629</v>
+        <v>0.49667104285010971</v>
       </c>
       <c r="M25">
-        <v>1.25034107070512</v>
+        <v>0.53458912640333434</v>
       </c>
       <c r="N25">
-        <v>1.39136208683369</v>
+        <v>0.62849210680277134</v>
       </c>
       <c r="O25">
-        <v>1.473406456493909</v>
+        <v>0.72270642175850686</v>
       </c>
       <c r="P25">
-        <v>1.530448475729935</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.81371526715121212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>0.09908485819786705</v>
+        <v>7.7110244856262403E-2</v>
       </c>
       <c r="C26">
-        <v>0.1550102912703344</v>
+        <v>0.14935455896626029</v>
       </c>
       <c r="D26">
-        <v>0.130508687804385</v>
+        <v>0.19783169670803399</v>
       </c>
       <c r="E26">
-        <v>0.1436021321381574</v>
+        <v>0.19028000553519031</v>
       </c>
       <c r="F26">
-        <v>0.2495483526458516</v>
+        <v>0.25277349242051822</v>
       </c>
       <c r="G26">
-        <v>0.2568331439127736</v>
+        <v>0.25752723646409759</v>
       </c>
       <c r="H26">
-        <v>0.2823304008278617</v>
+        <v>0.36187136445232593</v>
       </c>
       <c r="I26">
-        <v>0.3427872652500855</v>
+        <v>0.60902000226893227</v>
       </c>
       <c r="J26">
-        <v>0.3576756294268331</v>
+        <v>0.49969797530617271</v>
       </c>
       <c r="K26">
-        <v>0.4051328874395748</v>
+        <v>0.50029232025506265</v>
       </c>
       <c r="L26">
-        <v>0.4578310447640841</v>
+        <v>0.53780358671365058</v>
       </c>
       <c r="M26">
-        <v>0.4727284300345447</v>
+        <v>0.6295750594648285</v>
       </c>
       <c r="N26">
-        <v>0.5318862209634109</v>
+        <v>0.69422154655073931</v>
       </c>
       <c r="O26">
-        <v>0.6094031571596334</v>
+        <v>0.77205472378658191</v>
       </c>
       <c r="P26">
-        <v>0.6407557102476867</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.88513081346198774</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>0.162064690397171</v>
+        <v>7.8152574657144494E-2</v>
       </c>
       <c r="C27">
-        <v>0.3173437248974593</v>
+        <v>0.14938321533276441</v>
       </c>
       <c r="D27">
-        <v>0.1505623269748936</v>
+        <v>0.19366415639742901</v>
       </c>
       <c r="E27">
-        <v>0.1739876293255878</v>
+        <v>0.1693406164585976</v>
       </c>
       <c r="F27">
-        <v>0.2662164903437321</v>
+        <v>0.22731849602539159</v>
       </c>
       <c r="G27">
-        <v>0.3318972199762984</v>
+        <v>0.22331143460888411</v>
       </c>
       <c r="H27">
-        <v>0.403210064835113</v>
+        <v>0.25530528889346932</v>
       </c>
       <c r="I27">
-        <v>0.5372374205235193</v>
+        <v>0.43889653776172571</v>
       </c>
       <c r="J27">
-        <v>0.5698576597860578</v>
+        <v>0.35400386621464952</v>
       </c>
       <c r="K27">
-        <v>0.5959062082355955</v>
+        <v>0.33305079755485739</v>
       </c>
       <c r="L27">
-        <v>0.5800082036153495</v>
+        <v>0.32366519255368359</v>
       </c>
       <c r="M27">
-        <v>0.5778430484343948</v>
+        <v>0.37248378517256159</v>
       </c>
       <c r="N27">
-        <v>0.6028297601976964</v>
+        <v>0.37342392105766631</v>
       </c>
       <c r="O27">
-        <v>0.65564813045554</v>
+        <v>0.41714358107319649</v>
       </c>
       <c r="P27">
-        <v>0.6864757634299279</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.44276288661404739</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>0.0657076431518607</v>
+        <v>6.7611545247580979E-2</v>
       </c>
       <c r="C28">
-        <v>0.1260303665767638</v>
+        <v>0.1288075939348379</v>
       </c>
       <c r="D28">
-        <v>0.2173803768906239</v>
+        <v>0.22114552634240761</v>
       </c>
       <c r="E28">
-        <v>0.2095863268687895</v>
+        <v>0.2082285069249005</v>
       </c>
       <c r="F28">
-        <v>0.225428586586474</v>
+        <v>0.19713971084632151</v>
       </c>
       <c r="G28">
-        <v>0.2137667510850345</v>
+        <v>0.21125472450465579</v>
       </c>
       <c r="H28">
-        <v>0.3045445112060172</v>
+        <v>0.39031461877041218</v>
       </c>
       <c r="I28">
-        <v>0.4374643034388472</v>
+        <v>0.39632912127346293</v>
       </c>
       <c r="J28">
-        <v>0.4846305620308964</v>
+        <v>0.38424084271767728</v>
       </c>
       <c r="K28">
-        <v>0.4613885173323252</v>
+        <v>0.33891572962005911</v>
       </c>
       <c r="L28">
-        <v>0.4767105780082173</v>
+        <v>0.33733952121167893</v>
       </c>
       <c r="M28">
-        <v>0.5735437919186892</v>
+        <v>0.33397315253805843</v>
       </c>
       <c r="N28">
-        <v>0.679890046111939</v>
+        <v>0.37646302474162557</v>
       </c>
       <c r="O28">
-        <v>0.7591500910769088</v>
+        <v>0.41349316393029378</v>
       </c>
       <c r="P28">
-        <v>0.8686535830839194</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.45221181752857642</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>0.07468248532633809</v>
+        <v>7.1055240366653685E-2</v>
       </c>
       <c r="C29">
-        <v>0.1371200004455144</v>
+        <v>0.1358171191775433</v>
       </c>
       <c r="D29">
-        <v>0.2419853731229921</v>
+        <v>0.2338239982119901</v>
       </c>
       <c r="E29">
-        <v>0.2322481430235171</v>
+        <v>0.22067344656484991</v>
       </c>
       <c r="F29">
-        <v>0.2193739351826486</v>
+        <v>0.2050264915290248</v>
       </c>
       <c r="G29">
-        <v>0.2470775924296489</v>
+        <v>0.21571728729015421</v>
       </c>
       <c r="H29">
-        <v>0.5331670501908716</v>
+        <v>0.38788053899151509</v>
       </c>
       <c r="I29">
-        <v>0.5106857265402859</v>
+        <v>0.39455028513250329</v>
       </c>
       <c r="J29">
-        <v>0.5036161824609835</v>
+        <v>0.38367025586207681</v>
       </c>
       <c r="K29">
-        <v>0.4850284201896571</v>
+        <v>0.33822446652642879</v>
       </c>
       <c r="L29">
-        <v>0.4860207788085373</v>
+        <v>0.33771450128715552</v>
       </c>
       <c r="M29">
-        <v>0.5190219676826057</v>
+        <v>0.32303191329118541</v>
       </c>
       <c r="N29">
-        <v>0.5983961790846561</v>
+        <v>0.36388686519008018</v>
       </c>
       <c r="O29">
-        <v>0.6919327640742702</v>
+        <v>0.39558563839465288</v>
       </c>
       <c r="P29">
-        <v>0.7774953912884071</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.41460763718778149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>0.07758479740413199</v>
+        <v>7.372599432097951E-2</v>
       </c>
       <c r="C30">
-        <v>0.1477783894804692</v>
+        <v>0.13727794652396841</v>
       </c>
       <c r="D30">
-        <v>0.1954179996675209</v>
+        <v>0.22535131658833399</v>
       </c>
       <c r="E30">
-        <v>0.1865370027127151</v>
+        <v>0.21245012266571009</v>
       </c>
       <c r="F30">
-        <v>0.2578919042542827</v>
+        <v>0.19878943958167511</v>
       </c>
       <c r="G30">
-        <v>0.2590709905417385</v>
+        <v>0.21145401723817989</v>
       </c>
       <c r="H30">
-        <v>0.3802942786134278</v>
+        <v>0.37195493608929342</v>
       </c>
       <c r="I30">
-        <v>0.6124978789854455</v>
+        <v>0.37386607897504331</v>
       </c>
       <c r="J30">
-        <v>0.5100035050664896</v>
+        <v>0.37718059708004809</v>
       </c>
       <c r="K30">
-        <v>0.5096379848084001</v>
+        <v>0.32776588869253842</v>
       </c>
       <c r="L30">
-        <v>0.5436397633094951</v>
+        <v>0.32824089651657729</v>
       </c>
       <c r="M30">
-        <v>0.631651867612016</v>
+        <v>0.31649820415492391</v>
       </c>
       <c r="N30">
-        <v>0.699920596442291</v>
+        <v>0.3533828929029188</v>
       </c>
       <c r="O30">
-        <v>0.7830821826943373</v>
+        <v>0.37855406571059053</v>
       </c>
       <c r="P30">
-        <v>0.8949066584320959</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.39861166745584048</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>45</v>
       </c>
       <c r="B31">
-        <v>0.07737038176184435</v>
+        <v>6.5977827705335002E-2</v>
       </c>
       <c r="C31">
-        <v>0.1536156929089883</v>
+        <v>0.1228203900149018</v>
       </c>
       <c r="D31">
-        <v>0.1993376768644302</v>
+        <v>0.2176047639983778</v>
       </c>
       <c r="E31">
-        <v>0.1817555574917584</v>
+        <v>0.20085756805877761</v>
       </c>
       <c r="F31">
-        <v>0.2348279213259655</v>
+        <v>0.1912606202979103</v>
       </c>
       <c r="G31">
-        <v>0.2317595111294339</v>
+        <v>0.20255344714351539</v>
       </c>
       <c r="H31">
-        <v>0.2593564178992172</v>
+        <v>0.35326674654256401</v>
       </c>
       <c r="I31">
-        <v>0.4598751958399043</v>
+        <v>0.37925787972964958</v>
       </c>
       <c r="J31">
-        <v>0.3754785819258645</v>
+        <v>0.38324086871029173</v>
       </c>
       <c r="K31">
-        <v>0.3517958060790226</v>
+        <v>0.32421945884268938</v>
       </c>
       <c r="L31">
-        <v>0.3323929231091368</v>
+        <v>0.335116739318288</v>
       </c>
       <c r="M31">
-        <v>0.378375934324438</v>
+        <v>0.32776435127254377</v>
       </c>
       <c r="N31">
-        <v>0.3831709942382091</v>
+        <v>0.35603901837862723</v>
       </c>
       <c r="O31">
-        <v>0.4292543326040636</v>
+        <v>0.3888607671158355</v>
       </c>
       <c r="P31">
-        <v>0.4523595033560244</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.40196906333796772</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
       </c>
       <c r="B32">
-        <v>0.07113976980825909</v>
+        <v>6.7322441573736402E-2</v>
       </c>
       <c r="C32">
-        <v>0.1313181084993425</v>
+        <v>0.1319537797264152</v>
       </c>
       <c r="D32">
-        <v>0.2284926266424842</v>
+        <v>0.23042621378697731</v>
       </c>
       <c r="E32">
-        <v>0.2125582493868606</v>
+        <v>0.21741271199375861</v>
       </c>
       <c r="F32">
-        <v>0.2008162056782986</v>
+        <v>0.2005869610662824</v>
       </c>
       <c r="G32">
-        <v>0.2179788691036536</v>
+        <v>0.21165438095170691</v>
       </c>
       <c r="H32">
-        <v>0.3984366198419584</v>
+        <v>0.40194134243033469</v>
       </c>
       <c r="I32">
-        <v>0.3976997469546545</v>
+        <v>0.39830736220235369</v>
       </c>
       <c r="J32">
-        <v>0.3857470137800002</v>
+        <v>0.38680699323095608</v>
       </c>
       <c r="K32">
-        <v>0.3612108294753101</v>
+        <v>0.34851941372045803</v>
       </c>
       <c r="L32">
-        <v>0.346523784853895</v>
+        <v>0.35078350831485849</v>
       </c>
       <c r="M32">
-        <v>0.3435030300022969</v>
+        <v>0.35688538863613711</v>
       </c>
       <c r="N32">
-        <v>0.3746004528909045</v>
+        <v>0.40940252159817042</v>
       </c>
       <c r="O32">
-        <v>0.4168563035671892</v>
+        <v>0.46296287986689427</v>
       </c>
       <c r="P32">
-        <v>0.445447292660769</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.51528477258812666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
       </c>
       <c r="B33">
-        <v>0.07291164992198113</v>
+        <v>7.3283567382376971E-2</v>
       </c>
       <c r="C33">
-        <v>0.1363594970330548</v>
+        <v>0.13953312416834959</v>
       </c>
       <c r="D33">
-        <v>0.2318248385578142</v>
+        <v>0.23568790112540941</v>
       </c>
       <c r="E33">
-        <v>0.2164387876714763</v>
+        <v>0.22409447333079249</v>
       </c>
       <c r="F33">
-        <v>0.2026380757716171</v>
+        <v>0.2060027950325026</v>
       </c>
       <c r="G33">
-        <v>0.2094453963340044</v>
+        <v>0.22375327122677119</v>
       </c>
       <c r="H33">
-        <v>0.3800266282309782</v>
+        <v>0.40881025806066518</v>
       </c>
       <c r="I33">
-        <v>0.377875468546009</v>
+        <v>0.40634973738225372</v>
       </c>
       <c r="J33">
-        <v>0.3700411346476445</v>
+        <v>0.39607283492944279</v>
       </c>
       <c r="K33">
-        <v>0.3232703502189118</v>
+        <v>0.37003067185686911</v>
       </c>
       <c r="L33">
-        <v>0.3247536766155171</v>
+        <v>0.36513136744048391</v>
       </c>
       <c r="M33">
-        <v>0.3202848228116948</v>
+        <v>0.36658319872182132</v>
       </c>
       <c r="N33">
-        <v>0.3531826004839728</v>
+        <v>0.40867403300255822</v>
       </c>
       <c r="O33">
-        <v>0.3826042064094256</v>
+        <v>0.45645633912738592</v>
       </c>
       <c r="P33">
-        <v>0.4069067440229487</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.50754188519800902</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
       </c>
       <c r="B34">
-        <v>0.06729292389907937</v>
+        <v>7.142689497626592E-2</v>
       </c>
       <c r="C34">
-        <v>0.130144977018025</v>
+        <v>0.1396084386061972</v>
       </c>
       <c r="D34">
-        <v>0.2286429120521201</v>
+        <v>0.23668100575534379</v>
       </c>
       <c r="E34">
-        <v>0.2152697402200889</v>
+        <v>0.21917841449130751</v>
       </c>
       <c r="F34">
-        <v>0.195820673577404</v>
+        <v>0.20741801440785351</v>
       </c>
       <c r="G34">
-        <v>0.2054304411093182</v>
+        <v>0.22039324906096561</v>
       </c>
       <c r="H34">
-        <v>0.3731379758075806</v>
+        <v>0.40503115850967569</v>
       </c>
       <c r="I34">
-        <v>0.382621245177735</v>
+        <v>0.39443861961870408</v>
       </c>
       <c r="J34">
-        <v>0.3799216517510873</v>
+        <v>0.3857244701164062</v>
       </c>
       <c r="K34">
-        <v>0.336337589083875</v>
+        <v>0.37828542869031939</v>
       </c>
       <c r="L34">
-        <v>0.3334113508925771</v>
+        <v>0.3689395695379098</v>
       </c>
       <c r="M34">
-        <v>0.323078517808761</v>
+        <v>0.3675675546916124</v>
       </c>
       <c r="N34">
-        <v>0.3639164966006937</v>
+        <v>0.39722843034373179</v>
       </c>
       <c r="O34">
-        <v>0.3906883148304188</v>
+        <v>0.43563037281680789</v>
       </c>
       <c r="P34">
-        <v>0.4145929276672173</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.48091012407673028</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>49</v>
       </c>
       <c r="B35">
-        <v>0.07036447400021924</v>
+        <v>7.1376284106944327E-2</v>
       </c>
       <c r="C35">
-        <v>0.1370193552139108</v>
+        <v>0.13029648662115759</v>
       </c>
       <c r="D35">
-        <v>0.2329697309418059</v>
+        <v>0.2248489052276815</v>
       </c>
       <c r="E35">
-        <v>0.2173407358820298</v>
+        <v>0.21263889100487199</v>
       </c>
       <c r="F35">
-        <v>0.2053752854557724</v>
+        <v>0.19941806983336891</v>
       </c>
       <c r="G35">
-        <v>0.2162902393863992</v>
+        <v>0.21423372171048019</v>
       </c>
       <c r="H35">
-        <v>0.3708744471870631</v>
+        <v>0.39709021512743592</v>
       </c>
       <c r="I35">
-        <v>0.390640623115628</v>
+        <v>0.40060993276220619</v>
       </c>
       <c r="J35">
-        <v>0.3961199267927493</v>
+        <v>0.38927361068190319</v>
       </c>
       <c r="K35">
-        <v>0.3470206908936629</v>
+        <v>0.35464255172077591</v>
       </c>
       <c r="L35">
-        <v>0.3471870712000749</v>
+        <v>0.35940816507287632</v>
       </c>
       <c r="M35">
-        <v>0.3333134366057895</v>
+        <v>0.35134527042240249</v>
       </c>
       <c r="N35">
-        <v>0.3618442912181865</v>
+        <v>0.38724038260395421</v>
       </c>
       <c r="O35">
-        <v>0.3944303680798881</v>
+        <v>0.42728657249394553</v>
       </c>
       <c r="P35">
-        <v>0.4021954498267153</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.45839793619477298</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>50</v>
       </c>
       <c r="B36">
-        <v>0.07473056995451291</v>
+        <v>7.1910438596963139E-2</v>
       </c>
       <c r="C36">
-        <v>0.1453555661660083</v>
+        <v>0.13734913225016071</v>
       </c>
       <c r="D36">
-        <v>0.2389773942009833</v>
+        <v>0.22553599276935021</v>
       </c>
       <c r="E36">
-        <v>0.221996289675337</v>
+        <v>0.2134304523698754</v>
       </c>
       <c r="F36">
-        <v>0.213242358240208</v>
+        <v>0.2009681997886891</v>
       </c>
       <c r="G36">
-        <v>0.229941011046014</v>
+        <v>0.21388083837235619</v>
       </c>
       <c r="H36">
-        <v>0.4357483394134021</v>
+        <v>0.35862152318518548</v>
       </c>
       <c r="I36">
-        <v>0.4169324684827614</v>
+        <v>0.36994963542102521</v>
       </c>
       <c r="J36">
-        <v>0.4044252323491577</v>
+        <v>0.3729540977525449</v>
       </c>
       <c r="K36">
-        <v>0.367864191286109</v>
+        <v>0.32600389681240188</v>
       </c>
       <c r="L36">
-        <v>0.3636656687322294</v>
+        <v>0.32601773696020647</v>
       </c>
       <c r="M36">
-        <v>0.3549039319481165</v>
+        <v>0.32979623644844441</v>
       </c>
       <c r="N36">
-        <v>0.3994495361098805</v>
+        <v>0.34845753554255832</v>
       </c>
       <c r="O36">
-        <v>0.4515160552941572</v>
+        <v>0.38229155231999518</v>
       </c>
       <c r="P36">
-        <v>0.5089224217314907</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.39262322819675038</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>0.06712372035595555</v>
+        <v>0.1538675132009921</v>
       </c>
       <c r="C37">
-        <v>0.1272070966638671</v>
+        <v>0.34610654290578818</v>
       </c>
       <c r="D37">
-        <v>0.2208118833581632</v>
+        <v>0.29863784462761112</v>
       </c>
       <c r="E37">
-        <v>0.2114662720038405</v>
+        <v>0.32652233283138787</v>
       </c>
       <c r="F37">
-        <v>0.1933223498168175</v>
+        <v>0.53769882142521597</v>
       </c>
       <c r="G37">
-        <v>0.2114115948780264</v>
+        <v>0.56320075060278696</v>
       </c>
       <c r="H37">
-        <v>0.3979938204352155</v>
+        <v>0.57968717858466745</v>
       </c>
       <c r="I37">
-        <v>0.3951815105900818</v>
+        <v>0.57458932510841365</v>
       </c>
       <c r="J37">
-        <v>0.38562907164682</v>
+        <v>0.61430503098487144</v>
       </c>
       <c r="K37">
-        <v>0.3548210150440563</v>
+        <v>0.66821182300909066</v>
       </c>
       <c r="L37">
-        <v>0.3541082907230997</v>
+        <v>0.71641150358113981</v>
       </c>
       <c r="M37">
-        <v>0.3500119236604545</v>
+        <v>0.7865731693190432</v>
       </c>
       <c r="N37">
-        <v>0.3972751460511397</v>
+        <v>0.79397023091359042</v>
       </c>
       <c r="O37">
-        <v>0.4418152621044252</v>
+        <v>0.81149070036210935</v>
       </c>
       <c r="P37">
-        <v>0.500030138326546</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.82105931158794532</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>0.07097459395452993</v>
+        <v>0.1012087863483502</v>
       </c>
       <c r="C38">
-        <v>0.1341346374750732</v>
+        <v>0.25049618368661308</v>
       </c>
       <c r="D38">
-        <v>0.2276582597694148</v>
+        <v>0.25035323811055382</v>
       </c>
       <c r="E38">
-        <v>0.2080613621289629</v>
+        <v>0.27682310854199721</v>
       </c>
       <c r="F38">
-        <v>0.1940232340712603</v>
+        <v>0.45568766486769691</v>
       </c>
       <c r="G38">
-        <v>0.2046894891542711</v>
+        <v>0.35831297346051549</v>
       </c>
       <c r="H38">
-        <v>0.3786249718048775</v>
+        <v>0.27369562562943789</v>
       </c>
       <c r="I38">
-        <v>0.3808828426920138</v>
+        <v>0.32539293637620492</v>
       </c>
       <c r="J38">
-        <v>0.3697840949454629</v>
+        <v>0.39406450480492988</v>
       </c>
       <c r="K38">
-        <v>0.3495308207269456</v>
+        <v>0.46248329114775483</v>
       </c>
       <c r="L38">
-        <v>0.3489075195046826</v>
+        <v>0.51363873670453608</v>
       </c>
       <c r="M38">
-        <v>0.3467535350345985</v>
+        <v>0.55395568238789439</v>
       </c>
       <c r="N38">
-        <v>0.3840979831199897</v>
+        <v>0.59576339051631799</v>
       </c>
       <c r="O38">
-        <v>0.4135188558521105</v>
+        <v>0.62084816648265928</v>
       </c>
       <c r="P38">
-        <v>0.4693175063139187</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.63562397097688672</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>0.07312781216885936</v>
+        <v>9.7584640937117925E-2</v>
       </c>
       <c r="C39">
-        <v>0.1385980379417398</v>
+        <v>0.23146208933209031</v>
       </c>
       <c r="D39">
-        <v>0.2324817490564553</v>
+        <v>0.22144832048771279</v>
       </c>
       <c r="E39">
-        <v>0.2198006508246642</v>
+        <v>0.21441557995783089</v>
       </c>
       <c r="F39">
-        <v>0.2005136844959311</v>
+        <v>0.3452002119177916</v>
       </c>
       <c r="G39">
-        <v>0.2159977120725461</v>
+        <v>0.27678148285784282</v>
       </c>
       <c r="H39">
-        <v>0.3920246728198146</v>
+        <v>0.25986204316450939</v>
       </c>
       <c r="I39">
-        <v>0.3886624145198087</v>
+        <v>0.30794420469514711</v>
       </c>
       <c r="J39">
-        <v>0.3761863467946965</v>
+        <v>0.35861550923766028</v>
       </c>
       <c r="K39">
-        <v>0.3512552044744609</v>
+        <v>0.38579145745701438</v>
       </c>
       <c r="L39">
-        <v>0.3550666734474829</v>
+        <v>0.44380395114881471</v>
       </c>
       <c r="M39">
-        <v>0.3453046994587964</v>
+        <v>0.44947883485489382</v>
       </c>
       <c r="N39">
-        <v>0.3827495199269266</v>
+        <v>0.51218382246291783</v>
       </c>
       <c r="O39">
-        <v>0.4166101122363538</v>
+        <v>0.56009339351419618</v>
       </c>
       <c r="P39">
-        <v>0.4619329923383306</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.59021099502147023</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>54</v>
       </c>
       <c r="B40">
-        <v>0.07259329892980523</v>
+        <v>0.13246536416156801</v>
       </c>
       <c r="C40">
-        <v>0.1345921176015186</v>
+        <v>0.13019837980365079</v>
       </c>
       <c r="D40">
-        <v>0.224968976087299</v>
+        <v>0.2028283095123356</v>
       </c>
       <c r="E40">
-        <v>0.210736283312182</v>
+        <v>0.26710191077702172</v>
       </c>
       <c r="F40">
-        <v>0.1988677515589791</v>
+        <v>0.36684540396208609</v>
       </c>
       <c r="G40">
-        <v>0.2101804318076823</v>
+        <v>0.37625023089549398</v>
       </c>
       <c r="H40">
-        <v>0.3568091301924498</v>
+        <v>0.44687622722844689</v>
       </c>
       <c r="I40">
-        <v>0.3678346252985997</v>
+        <v>0.54469368629378034</v>
       </c>
       <c r="J40">
-        <v>0.3650958239194341</v>
+        <v>0.60177163193911831</v>
       </c>
       <c r="K40">
-        <v>0.3101493435757393</v>
+        <v>0.61626663354405409</v>
       </c>
       <c r="L40">
-        <v>0.3245309266150806</v>
+        <v>0.64484755620050738</v>
       </c>
       <c r="M40">
-        <v>0.3207938442842869</v>
+        <v>0.64798783407778793</v>
       </c>
       <c r="N40">
-        <v>0.3450453601060295</v>
+        <v>0.68546577976478507</v>
       </c>
       <c r="O40">
-        <v>0.3775586785898579</v>
+        <v>0.73200898549382742</v>
       </c>
       <c r="P40">
-        <v>0.3885501509408991</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.81550728517144966</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>0.1490655056232215</v>
+        <v>0.17010033724064261</v>
       </c>
       <c r="C41">
-        <v>0.3365963060440385</v>
+        <v>0.48603031161388771</v>
       </c>
       <c r="D41">
-        <v>0.2970372341995523</v>
+        <v>0.48303284490143428</v>
       </c>
       <c r="E41">
-        <v>0.3247669300079283</v>
+        <v>0.57085893731848936</v>
       </c>
       <c r="F41">
-        <v>0.529167099466423</v>
+        <v>0.59993319938251322</v>
       </c>
       <c r="G41">
-        <v>0.5595924198457292</v>
+        <v>0.6330275610771432</v>
       </c>
       <c r="H41">
-        <v>0.5705356289432367</v>
+        <v>0.6691396824905318</v>
       </c>
       <c r="I41">
-        <v>0.5652848001488242</v>
+        <v>0.67058734917407059</v>
       </c>
       <c r="J41">
-        <v>0.6047920620891053</v>
+        <v>0.74235552667456706</v>
       </c>
       <c r="K41">
-        <v>0.6569646051951773</v>
+        <v>0.80390938556342717</v>
       </c>
       <c r="L41">
-        <v>0.7122697319011302</v>
+        <v>0.84047740288633555</v>
       </c>
       <c r="M41">
-        <v>0.7821650892338845</v>
+        <v>0.90175627515432655</v>
       </c>
       <c r="N41">
-        <v>0.790638522678474</v>
+        <v>0.97934770721495801</v>
       </c>
       <c r="O41">
-        <v>0.8058037141067239</v>
+        <v>1.0079033814068119</v>
       </c>
       <c r="P41">
-        <v>0.8168459668839659</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>1.042065550301019</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>56</v>
       </c>
       <c r="B42">
-        <v>0.09514104987411152</v>
+        <v>6.2492141205943222E-2</v>
       </c>
       <c r="C42">
-        <v>0.2447027264272521</v>
+        <v>0.62593980900715429</v>
       </c>
       <c r="D42">
-        <v>0.2467679860347173</v>
+        <v>0.56611661177848427</v>
       </c>
       <c r="E42">
-        <v>0.2753739660144459</v>
+        <v>0.43444416179879919</v>
       </c>
       <c r="F42">
-        <v>0.4583491440772377</v>
+        <v>0.42125581024770159</v>
       </c>
       <c r="G42">
-        <v>0.3594137291615069</v>
+        <v>0.44633928970059378</v>
       </c>
       <c r="H42">
-        <v>0.2799617608452065</v>
+        <v>0.42065227833535068</v>
       </c>
       <c r="I42">
-        <v>0.3318537540065944</v>
+        <v>0.44589414019002149</v>
       </c>
       <c r="J42">
-        <v>0.4038340993871229</v>
+        <v>0.49895116614667362</v>
       </c>
       <c r="K42">
-        <v>0.4780321290321684</v>
+        <v>0.51765988369399785</v>
       </c>
       <c r="L42">
-        <v>0.5281896288282524</v>
+        <v>0.54821377433876795</v>
       </c>
       <c r="M42">
-        <v>0.5710940168667762</v>
+        <v>0.60879335596831852</v>
       </c>
       <c r="N42">
-        <v>0.6073802445048522</v>
+        <v>0.63945575105746699</v>
       </c>
       <c r="O42">
-        <v>0.6281179758646911</v>
+        <v>0.64756008355326899</v>
       </c>
       <c r="P42">
-        <v>0.6393305965373263</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.68894601233440111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>57</v>
       </c>
       <c r="B43">
-        <v>0.09822444421045938</v>
+        <v>0.1009283957905875</v>
       </c>
       <c r="C43">
-        <v>0.2271004104326133</v>
+        <v>0.23873296930550161</v>
       </c>
       <c r="D43">
-        <v>0.2171616570198887</v>
+        <v>0.36832181484635518</v>
       </c>
       <c r="E43">
-        <v>0.2235192977387296</v>
+        <v>0.44415814434006068</v>
       </c>
       <c r="F43">
-        <v>0.3460470624203866</v>
+        <v>0.35456089466893581</v>
       </c>
       <c r="G43">
-        <v>0.2839446117292471</v>
+        <v>0.35586436893098627</v>
       </c>
       <c r="H43">
-        <v>0.2584892996416455</v>
+        <v>0.39495976908638569</v>
       </c>
       <c r="I43">
-        <v>0.3064118626029327</v>
+        <v>0.44085558054261592</v>
       </c>
       <c r="J43">
-        <v>0.3584702385853312</v>
+        <v>0.53793169353912118</v>
       </c>
       <c r="K43">
-        <v>0.3875597346435117</v>
+        <v>0.53690171686707544</v>
       </c>
       <c r="L43">
-        <v>0.4343642889962925</v>
+        <v>0.56228541521681774</v>
       </c>
       <c r="M43">
-        <v>0.4449166534126943</v>
+        <v>0.58879631361247431</v>
       </c>
       <c r="N43">
-        <v>0.502602982482803</v>
+        <v>0.62476254539728093</v>
       </c>
       <c r="O43">
-        <v>0.554991258481824</v>
+        <v>0.65868716759245438</v>
       </c>
       <c r="P43">
-        <v>0.5851018650879898</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.1429191901859554</v>
-      </c>
-      <c r="C44">
-        <v>0.1382917768582791</v>
-      </c>
-      <c r="D44">
-        <v>0.1978290497321425</v>
-      </c>
-      <c r="E44">
-        <v>0.2684406729439894</v>
-      </c>
-      <c r="F44">
-        <v>0.3693640016875881</v>
-      </c>
-      <c r="G44">
-        <v>0.3740444685379316</v>
-      </c>
-      <c r="H44">
-        <v>0.4506567953429675</v>
-      </c>
-      <c r="I44">
-        <v>0.5476639537084137</v>
-      </c>
-      <c r="J44">
-        <v>0.6118992102428739</v>
-      </c>
-      <c r="K44">
-        <v>0.625927181603734</v>
-      </c>
-      <c r="L44">
-        <v>0.658171421114172</v>
-      </c>
-      <c r="M44">
-        <v>0.6650683833284702</v>
-      </c>
-      <c r="N44">
-        <v>0.7042118087948535</v>
-      </c>
-      <c r="O44">
-        <v>0.7502404264802125</v>
-      </c>
-      <c r="P44">
-        <v>0.8240497012345671</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.1705025651057053</v>
-      </c>
-      <c r="C45">
-        <v>0.5079261556435932</v>
-      </c>
-      <c r="D45">
-        <v>0.497343947703733</v>
-      </c>
-      <c r="E45">
-        <v>0.5828731884114324</v>
-      </c>
-      <c r="F45">
-        <v>0.6204915893506289</v>
-      </c>
-      <c r="G45">
-        <v>0.6480264947355574</v>
-      </c>
-      <c r="H45">
-        <v>0.6930919175501906</v>
-      </c>
-      <c r="I45">
-        <v>0.6965361541665379</v>
-      </c>
-      <c r="J45">
-        <v>0.7560593751624461</v>
-      </c>
-      <c r="K45">
-        <v>0.8206776079059647</v>
-      </c>
-      <c r="L45">
-        <v>0.8518367692122908</v>
-      </c>
-      <c r="M45">
-        <v>0.9130858772949257</v>
-      </c>
-      <c r="N45">
-        <v>0.9922935037552721</v>
-      </c>
-      <c r="O45">
-        <v>1.022746503372373</v>
-      </c>
-      <c r="P45">
-        <v>1.063017939789391</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.05785073043397995</v>
-      </c>
-      <c r="C46">
-        <v>0.6065384398387014</v>
-      </c>
-      <c r="D46">
-        <v>0.5337321706532545</v>
-      </c>
-      <c r="E46">
-        <v>0.4140207501100424</v>
-      </c>
-      <c r="F46">
-        <v>0.4127102312907327</v>
-      </c>
-      <c r="G46">
-        <v>0.442262418765104</v>
-      </c>
-      <c r="H46">
-        <v>0.4175135219742113</v>
-      </c>
-      <c r="I46">
-        <v>0.4461747467248362</v>
-      </c>
-      <c r="J46">
-        <v>0.4926270002130788</v>
-      </c>
-      <c r="K46">
-        <v>0.5121428708115358</v>
-      </c>
-      <c r="L46">
-        <v>0.5452009976370191</v>
-      </c>
-      <c r="M46">
-        <v>0.6095662719269516</v>
-      </c>
-      <c r="N46">
-        <v>0.6370916423768997</v>
-      </c>
-      <c r="O46">
-        <v>0.6503788765778507</v>
-      </c>
-      <c r="P46">
-        <v>0.6919394556755433</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.110541872057105</v>
-      </c>
-      <c r="C47">
-        <v>0.2505289486349513</v>
-      </c>
-      <c r="D47">
-        <v>0.3843532461328641</v>
-      </c>
-      <c r="E47">
-        <v>0.4660579052871431</v>
-      </c>
-      <c r="F47">
-        <v>0.3608401355829365</v>
-      </c>
-      <c r="G47">
-        <v>0.3679600456349216</v>
-      </c>
-      <c r="H47">
-        <v>0.39836150241081</v>
-      </c>
-      <c r="I47">
-        <v>0.4492293443922828</v>
-      </c>
-      <c r="J47">
-        <v>0.5439030485689027</v>
-      </c>
-      <c r="K47">
-        <v>0.5503002294094866</v>
-      </c>
-      <c r="L47">
-        <v>0.5779980109062857</v>
-      </c>
-      <c r="M47">
-        <v>0.6056296989672671</v>
-      </c>
-      <c r="N47">
-        <v>0.6486172670868845</v>
-      </c>
-      <c r="O47">
-        <v>0.6798944894643667</v>
-      </c>
-      <c r="P47">
-        <v>0.7187812332221581</v>
+        <v>0.69030822974361128</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:P43">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0.2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>